--- a/Sender Gmail Emails/CursoPLFrankPt2 - Aviso - Parte-2/Datos/Lista de Invitados.xlsx
+++ b/Sender Gmail Emails/CursoPLFrankPt2 - Aviso - Parte-2/Datos/Lista de Invitados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cinvestav365-my.sharepoint.com/personal/edgar_agustin_cinvestav_mx/Documents/Documentos/GitHub/Python/Sender Gmail Emails/CursoPLFrankPt2 - Aviso/Datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cinvestav365-my.sharepoint.com/personal/edgar_agustin_cinvestav_mx/Documents/Documentos/GitHub/Python/Sender Gmail Emails/CursoPLFrankPt2 - Aviso - Parte-2/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32FD59B2-D9CC-47CE-9D4D-02E9FFE0F239}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01CAE6D6-4A1D-40DF-8AA3-3BA126D73887}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57CD9F27-ED92-4D92-97BD-4EB2C2546C2C}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="819">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -61,6 +61,9 @@
     <t>Chandel</t>
   </si>
   <si>
+    <t>chandel.abhishek@cinvestav.mx</t>
+  </si>
+  <si>
     <t>Presencial</t>
   </si>
   <si>
@@ -73,12 +76,18 @@
     <t>Cirilo Martínez</t>
   </si>
   <si>
+    <t>abrahamcirilo040@gmail.com</t>
+  </si>
+  <si>
     <t>Martínez</t>
   </si>
   <si>
     <t>Méndez Reséndiz</t>
   </si>
   <si>
+    <t>abraham.mendez@cimav.edu.mx</t>
+  </si>
+  <si>
     <t>Virtual</t>
   </si>
   <si>
@@ -91,6 +100,9 @@
     <t>Martinez Castillo</t>
   </si>
   <si>
+    <t>amartinezc1510@alumno.ipn.mx</t>
+  </si>
+  <si>
     <t>IPN</t>
   </si>
   <si>
@@ -100,6 +112,9 @@
     <t>Medina Limón</t>
   </si>
   <si>
+    <t>addimedina@gmail.com</t>
+  </si>
+  <si>
     <t>Instituto Politécnico Nacional - UPIBI</t>
   </si>
   <si>
@@ -109,6 +124,9 @@
     <t>López Sánchez</t>
   </si>
   <si>
+    <t>adlopez0587@gmail.com</t>
+  </si>
+  <si>
     <t>Uptap</t>
   </si>
   <si>
@@ -118,12 +136,18 @@
     <t>Solis Jardon</t>
   </si>
   <si>
+    <t>soja960812@gmail.com</t>
+  </si>
+  <si>
     <t>Adriana</t>
   </si>
   <si>
     <t>Cruz Enríquez</t>
   </si>
   <si>
+    <t>cruzadriana@uas.edu.mx</t>
+  </si>
+  <si>
     <t>Universidad Autónoma de Sinaloa</t>
   </si>
   <si>
@@ -133,6 +157,9 @@
     <t>Camacho Sánchez</t>
   </si>
   <si>
+    <t>aileencamachosanchez420@gmail.com</t>
+  </si>
+  <si>
     <t>UPIITA</t>
   </si>
   <si>
@@ -142,6 +169,9 @@
     <t>Santiago Cuevas</t>
   </si>
   <si>
+    <t>alan_javier_sc@hotmail.com</t>
+  </si>
+  <si>
     <t>UNAM</t>
   </si>
   <si>
@@ -151,6 +181,9 @@
     <t>Cruz Sánchez</t>
   </si>
   <si>
+    <t>alejandra.cruz5842@alumnos.udg.mx</t>
+  </si>
+  <si>
     <t>Universidad de Guadalajara</t>
   </si>
   <si>
@@ -160,18 +193,27 @@
     <t>Mendoza Villa</t>
   </si>
   <si>
+    <t>aledlg56@gmail.com</t>
+  </si>
+  <si>
     <t>Alejandro Iván</t>
   </si>
   <si>
     <t>Cuesta Balderas</t>
   </si>
   <si>
+    <t>alexivan11235@hotmail.com</t>
+  </si>
+  <si>
     <t>Alexander</t>
   </si>
   <si>
     <t>Farías Villa</t>
   </si>
   <si>
+    <t>Alexfarias665@gmail.com</t>
+  </si>
+  <si>
     <t>Tecnológico nacional de México campus Tuxtla Gutiérrez</t>
   </si>
   <si>
@@ -181,6 +223,9 @@
     <t>Hernández Laguna</t>
   </si>
   <si>
+    <t>karhen.laguna.9909@gmail.com</t>
+  </si>
+  <si>
     <t>ESIQIE</t>
   </si>
   <si>
@@ -190,12 +235,18 @@
     <t>Suárez Sánchez</t>
   </si>
   <si>
+    <t>asuarezs0811@gmail.com</t>
+  </si>
+  <si>
     <t>Andrei</t>
   </si>
   <si>
     <t>Gómez Mendoza</t>
   </si>
   <si>
+    <t>a.mendoza.photonics@gmail.com</t>
+  </si>
+  <si>
     <t>ESIME</t>
   </si>
   <si>
@@ -205,12 +256,18 @@
     <t>Morales Estrada</t>
   </si>
   <si>
+    <t>andresmo1987@hotmail.com</t>
+  </si>
+  <si>
     <t>Andres Ambrocio</t>
   </si>
   <si>
     <t>Zapoteco Cuaxinque</t>
   </si>
   <si>
+    <t>azapotecoc2100@alumno.ipn.mx</t>
+  </si>
+  <si>
     <t>ESIME-CU</t>
   </si>
   <si>
@@ -220,21 +277,33 @@
     <t>Fentanes Sánchez</t>
   </si>
   <si>
+    <t>angel.010600@gmail.com</t>
+  </si>
+  <si>
     <t>Hernandez Gomez Tagle</t>
   </si>
   <si>
+    <t>sergioangel25082005@gmail.com</t>
+  </si>
+  <si>
     <t>Angela Giselle</t>
   </si>
   <si>
     <t>Rosales Garza</t>
   </si>
   <si>
+    <t>A01572225@tec.mx</t>
+  </si>
+  <si>
     <t>Ariadna Zoe</t>
   </si>
   <si>
     <t>Rosales Domínguez</t>
   </si>
   <si>
+    <t>zoe.rosales.0630@gmail.com</t>
+  </si>
+  <si>
     <t>TECNOLÓGICO DE ESTUDIOS SUPERIORES CHICOLOAPAN</t>
   </si>
   <si>
@@ -244,24 +313,36 @@
     <t>Domínguez García</t>
   </si>
   <si>
+    <t>armando.dominguez@cimav.edu.mx</t>
+  </si>
+  <si>
     <t>Armando Edgar</t>
   </si>
   <si>
     <t>Castillo García</t>
   </si>
   <si>
+    <t>armando.castillo@cimav.edu.mx</t>
+  </si>
+  <si>
     <t>Arturo</t>
   </si>
   <si>
     <t>Hernández Hernández</t>
   </si>
   <si>
+    <t>arturo_hernandez@uaeh.edu.mx</t>
+  </si>
+  <si>
     <t>Axel</t>
   </si>
   <si>
     <t>Macías García</t>
   </si>
   <si>
+    <t>axelmacias.pi@gmail.com</t>
+  </si>
+  <si>
     <t>Instituto de ingeniería</t>
   </si>
   <si>
@@ -271,6 +352,9 @@
     <t>Ortiz Atondo</t>
   </si>
   <si>
+    <t>axel.ortiz@cimav.edu.mx</t>
+  </si>
+  <si>
     <t>Centro de Investigación en Materiales Avanzados S. C. subsede Monterrey</t>
   </si>
   <si>
@@ -280,6 +364,9 @@
     <t>García Cruz</t>
   </si>
   <si>
+    <t>azalea91garcia@gmail.com</t>
+  </si>
+  <si>
     <t>Instituto Tecnológico de Tuxtla Gutiérrez</t>
   </si>
   <si>
@@ -289,18 +376,27 @@
     <t>Marún</t>
   </si>
   <si>
+    <t>A01412942@tec.mx</t>
+  </si>
+  <si>
     <t>Beatriz Elena</t>
   </si>
   <si>
     <t>Bonola Barrientos</t>
   </si>
   <si>
+    <t>betybonola27@gmail.com</t>
+  </si>
+  <si>
     <t>Belem</t>
   </si>
   <si>
     <t>Garcés Martínez</t>
   </si>
   <si>
+    <t>20254182@uatx.mx</t>
+  </si>
+  <si>
     <t>UNIVERSIDAD AUTÓNOMA DE TLAXCALA</t>
   </si>
   <si>
@@ -310,6 +406,9 @@
     <t>Rodriguez Garcia</t>
   </si>
   <si>
+    <t>bibiana.rodriguez@cinvestav.mx</t>
+  </si>
+  <si>
     <t>CINVESTAV</t>
   </si>
   <si>
@@ -319,132 +418,204 @@
     <t>Pedroza Rojas</t>
   </si>
   <si>
+    <t>brandonrpce@gmail.com</t>
+  </si>
+  <si>
     <t>Braulio</t>
   </si>
   <si>
     <t>Palacios Márquez</t>
   </si>
   <si>
+    <t>bpalacios@inaoep.mx</t>
+  </si>
+  <si>
     <t>Carlo</t>
   </si>
   <si>
     <t>Mortera Ahuet</t>
   </si>
   <si>
+    <t>carlomat0302@gmail.com</t>
+  </si>
+  <si>
     <t>Carlos</t>
   </si>
   <si>
     <t>Cruz Val</t>
   </si>
   <si>
+    <t>carloscruzval10@gmail.com</t>
+  </si>
+  <si>
     <t>Carlos Arturo</t>
   </si>
   <si>
     <t>García González</t>
   </si>
   <si>
+    <t>carlosarturogargon36@gmail.com</t>
+  </si>
+  <si>
     <t>Carlos Ernesto</t>
   </si>
   <si>
     <t>Ávila Crisóstomo</t>
   </si>
   <si>
+    <t>ceac0687@gmail.com</t>
+  </si>
+  <si>
     <t>Carmen Anayely</t>
   </si>
   <si>
     <t>Cruz Galván</t>
   </si>
   <si>
+    <t>anazura.25@gmail.com</t>
+  </si>
+  <si>
     <t>Cassandra</t>
   </si>
   <si>
     <t>González Armendáriz</t>
   </si>
   <si>
+    <t>csndr.ga.21@gmail.com</t>
+  </si>
+  <si>
     <t>Cecilia Mabel</t>
   </si>
   <si>
     <t>Pérez Rivas</t>
   </si>
   <si>
+    <t>mabel.przr@gmail.com</t>
+  </si>
+  <si>
     <t>César</t>
   </si>
   <si>
     <t>Rosales Martínez</t>
   </si>
   <si>
+    <t>c.rosalesm97@gmail.com</t>
+  </si>
+  <si>
     <t>López Galván</t>
   </si>
   <si>
+    <t>cesarlg060@gmail.com</t>
+  </si>
+  <si>
     <t>Christian Alejandro</t>
   </si>
   <si>
     <t>Mercado Ornelas</t>
   </si>
   <si>
+    <t>christian.mercado@upslp.edu.mx</t>
+  </si>
+  <si>
     <t>Christian Jair</t>
   </si>
   <si>
     <t>Nuñez Delgado</t>
   </si>
   <si>
+    <t>cnunezd2000@alumno.ipn.mx</t>
+  </si>
+  <si>
     <t>Cirino</t>
   </si>
   <si>
     <t>Rivera Bautista</t>
   </si>
   <si>
+    <t>cirino12oct@gmail.com</t>
+  </si>
+  <si>
     <t>Claudia Nancy</t>
   </si>
   <si>
     <t>Ortega Aceves</t>
   </si>
   <si>
+    <t>claus.kali@gmail.com</t>
+  </si>
+  <si>
     <t>Cristian Brayan</t>
   </si>
   <si>
     <t>Palacios Cabrera</t>
   </si>
   <si>
+    <t>palacios_cabrera@hotmail.com</t>
+  </si>
+  <si>
     <t>Cristian Francisco</t>
   </si>
   <si>
     <t>Sánchez Reyes</t>
   </si>
   <si>
+    <t>layanux@hotmail.com</t>
+  </si>
+  <si>
     <t>Daniel</t>
   </si>
   <si>
     <t>García Juárez</t>
   </si>
   <si>
+    <t>daniel.garcia7863@alumnos.udg.mx</t>
+  </si>
+  <si>
     <t>Hernández Rivera</t>
   </si>
   <si>
+    <t>daniel.rivera@teschic.edu.mx</t>
+  </si>
+  <si>
     <t>García Garbuno</t>
   </si>
   <si>
+    <t>danno.g.g72@gmail.com</t>
+  </si>
+  <si>
     <t>Daniela</t>
   </si>
   <si>
     <t>Lucio Rosales</t>
   </si>
   <si>
+    <t>Daniela.lucio@cimav.edu.mx</t>
+  </si>
+  <si>
     <t>Cardenas Martinez</t>
   </si>
   <si>
+    <t>Danicdsmtz999@gmail.com</t>
+  </si>
+  <si>
     <t>Daniela Soledad</t>
   </si>
   <si>
     <t>Huerta José</t>
   </si>
   <si>
+    <t>dansolhuertaj@gmail.com</t>
+  </si>
+  <si>
     <t>Danna Paola</t>
   </si>
   <si>
     <t>Rosales Figueroa</t>
   </si>
   <si>
+    <t>pao.rofi27@gmail.com</t>
+  </si>
+  <si>
     <t>Dario Alessandro</t>
   </si>
   <si>
@@ -457,82 +628,115 @@
     <t>Reyes Trejo</t>
   </si>
   <si>
+    <t>Davidrt02@outlook.com</t>
+  </si>
+  <si>
     <t>Dayana</t>
   </si>
   <si>
     <t>Martínez Miranda</t>
   </si>
   <si>
+    <t>a01612915@tec.mx</t>
+  </si>
+  <si>
     <t>Diana Marcela</t>
   </si>
   <si>
     <t>Rojas Campiño</t>
   </si>
   <si>
+    <t>diana.rojasc@cinvestav.mx</t>
+  </si>
+  <si>
     <t>Diana Sofía Michell</t>
   </si>
   <si>
     <t>Flores Saldaña</t>
   </si>
   <si>
+    <t>dianasofiamichell@gmail.com</t>
+  </si>
+  <si>
     <t>Diana Wendolyn</t>
   </si>
   <si>
     <t>Alonso Rodríguez</t>
   </si>
   <si>
+    <t>diana.alonso1982@alumnos.udg.mx</t>
+  </si>
+  <si>
     <t>Diego Alberto</t>
   </si>
   <si>
     <t>Velázquez Pérez</t>
   </si>
   <si>
+    <t>velazquezalberto432@gmail.com</t>
+  </si>
+  <si>
     <t>Diego Josué</t>
   </si>
   <si>
     <t>Martínez Méndez</t>
   </si>
   <si>
+    <t>diego.martinez@chicoloapan.tecnm.mx</t>
+  </si>
+  <si>
     <t>Disnel</t>
   </si>
   <si>
     <t>Ferrera Carracedo</t>
   </si>
   <si>
+    <t>disfer96@gmail.com</t>
+  </si>
+  <si>
     <t>Edgar</t>
   </si>
   <si>
     <t>López Luna</t>
   </si>
   <si>
+    <t>edgar.luna@uaslp.mx</t>
+  </si>
+  <si>
     <t>Eduardo</t>
   </si>
   <si>
     <t>Merino Montes</t>
   </si>
   <si>
+    <t>emerinom1500@alumno.ipn.mx</t>
+  </si>
+  <si>
     <t>Eduardo Ismael</t>
   </si>
   <si>
     <t>Martínez García</t>
   </si>
   <si>
+    <t>eduardo.martinez.garcia@upvm.edu.mx</t>
+  </si>
+  <si>
     <t>Elba Cinthya</t>
   </si>
   <si>
     <t>García Estrada</t>
   </si>
   <si>
+    <t>ingcin@hotmail.com</t>
+  </si>
+  <si>
     <t>Elder Alejandro</t>
   </si>
   <si>
     <t>Meza Ramírez</t>
   </si>
   <si>
-    <t>Eleazar</t>
-  </si>
-  <si>
-    <t>Becerril</t>
+    <t>elder.meza3439@alumnos.udg.mx</t>
   </si>
   <si>
     <t>Elsa Lucía</t>
@@ -541,126 +745,192 @@
     <t>Soto Bermúdez</t>
   </si>
   <si>
+    <t>luciasoto@live.com</t>
+  </si>
+  <si>
     <t>Emiliano</t>
   </si>
   <si>
     <t>Rodríguez Peña</t>
   </si>
   <si>
+    <t>emiliano_acolatronic@hotmail.com</t>
+  </si>
+  <si>
     <t>Emilio</t>
   </si>
   <si>
     <t>Villegas Monroy</t>
   </si>
   <si>
+    <t>villegas.monroy.emilio@gmail.com</t>
+  </si>
+  <si>
     <t>Emilio Antonio</t>
   </si>
   <si>
     <t>Cortés Yáñez</t>
   </si>
   <si>
+    <t>cortesemilio.y@gmail.com</t>
+  </si>
+  <si>
     <t>ENRIQUE</t>
   </si>
   <si>
     <t>CAMPOS GONZALEZ</t>
   </si>
   <si>
+    <t>enriquecampos82@gmail.com</t>
+  </si>
+  <si>
     <t>Erick</t>
   </si>
   <si>
     <t>Rodríguez Martínez</t>
   </si>
   <si>
+    <t>rodriguezmartinezerick04ipn@gmail.com</t>
+  </si>
+  <si>
     <t>Erik Antonio</t>
   </si>
   <si>
     <t>Arroyo Sosa</t>
   </si>
   <si>
+    <t>erikantonioarroyososa@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Erika </t>
   </si>
   <si>
     <t>Juarez Hernandez</t>
   </si>
   <si>
+    <t>eri.juarezhrdz@outlook.com</t>
+  </si>
+  <si>
     <t>Esmeralda Lizet</t>
   </si>
   <si>
     <t>Martínez Piñeiro</t>
   </si>
   <si>
+    <t>esmeraldamartinez@ciencias.unam.mx</t>
+  </si>
+  <si>
     <t>Evelin Itzel</t>
   </si>
   <si>
     <t>Hernández Rodríguez</t>
   </si>
   <si>
+    <t>ehernandezr2300@alumno.ipn.mx</t>
+  </si>
+  <si>
     <t>Fernanda</t>
   </si>
   <si>
     <t>Reyes Guerrero</t>
   </si>
   <si>
+    <t>fernandareyesguerrero470@gmail.com</t>
+  </si>
+  <si>
     <t>Fernando</t>
   </si>
   <si>
     <t>Avalos</t>
   </si>
   <si>
+    <t>Fernando.avalos@cinvestav.mx</t>
+  </si>
+  <si>
     <t>Fernando Iván</t>
   </si>
   <si>
+    <t>fernando.igjuarez@gmail.com</t>
+  </si>
+  <si>
     <t>Francisco Javier</t>
   </si>
   <si>
     <t>Espinoza Chavez</t>
   </si>
   <si>
+    <t>javierespinoza.facite@uas.edu.mx</t>
+  </si>
+  <si>
     <t>Gabriela Mariela</t>
   </si>
   <si>
     <t>Reyes Chaparro</t>
   </si>
   <si>
+    <t>mreys.gaby@gmail.com</t>
+  </si>
+  <si>
     <t>Genaro</t>
   </si>
   <si>
     <t>López Gamboa</t>
   </si>
   <si>
+    <t>genaro.lopez11@yahoo.com</t>
+  </si>
+  <si>
     <t>Georgia Ann</t>
   </si>
   <si>
     <t>Rascón Ramírez</t>
   </si>
   <si>
+    <t>anarazcon2004@gmail.com</t>
+  </si>
+  <si>
     <t>GILBERTO</t>
   </si>
   <si>
     <t>CASTAÑEDA BARRERA</t>
   </si>
   <si>
+    <t>gilbert.castbar@gmail.com</t>
+  </si>
+  <si>
     <t>Gilberto Gamaliel</t>
   </si>
   <si>
     <t>Díaz Monroy</t>
   </si>
   <si>
+    <t>gilberto.diaz@cinvestav.mx</t>
+  </si>
+  <si>
     <t>Gloria Isabel</t>
   </si>
   <si>
     <t>Siller Monroy</t>
   </si>
   <si>
+    <t>isabesill@gmail.com</t>
+  </si>
+  <si>
     <t>Gustavo</t>
   </si>
   <si>
     <t>Coronel Corte</t>
   </si>
   <si>
+    <t>gccorte@azc.uam.mx</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gutierrez Hernandez Eduardo Alfredo </t>
   </si>
   <si>
+    <t>lgutierrez33.253@gmail.com</t>
+  </si>
+  <si>
     <t>presencial</t>
   </si>
   <si>
@@ -673,180 +943,273 @@
     <t>Bermon Bayona</t>
   </si>
   <si>
+    <t>yessbermon@gmail.com</t>
+  </si>
+  <si>
     <t>Hector Leonardo</t>
   </si>
   <si>
     <t>Anaya Aduna</t>
   </si>
   <si>
+    <t>leo.aduna1998@gmail.com</t>
+  </si>
+  <si>
     <t>Hernandez Morales Yael Gabriel</t>
   </si>
   <si>
+    <t>yagahmo2047@gmail.com</t>
+  </si>
+  <si>
     <t>Hugo</t>
   </si>
   <si>
     <t>Rubio Romero</t>
   </si>
   <si>
+    <t>hrubior1800@gmail.com</t>
+  </si>
+  <si>
     <t>Ian Diego</t>
   </si>
   <si>
     <t>De los Santos Nolasco</t>
   </si>
   <si>
+    <t>delossantosnolascoiandiego@gmail.com</t>
+  </si>
+  <si>
     <t>Ilse</t>
   </si>
   <si>
     <t>Romero Grandvallet</t>
   </si>
   <si>
+    <t>ilsegrandvallet7822@gmail.com</t>
+  </si>
+  <si>
     <t>Indira</t>
   </si>
   <si>
     <t>Torres Sandoval</t>
   </si>
   <si>
+    <t>intorres@ipn.mx</t>
+  </si>
+  <si>
     <t>Irving</t>
   </si>
   <si>
     <t>Ramírez Aguirre</t>
   </si>
   <si>
+    <t>irvingraguirre@hotmail.com</t>
+  </si>
+  <si>
     <t>Issis Claudette</t>
   </si>
   <si>
     <t>Romero Ibarra</t>
   </si>
   <si>
+    <t>iromero@ipn.mx</t>
+  </si>
+  <si>
     <t>Itzany Janet</t>
   </si>
   <si>
     <t>De la Cruz Salazar</t>
   </si>
   <si>
+    <t>itzanys@gmail.com</t>
+  </si>
+  <si>
     <t>Itzel</t>
   </si>
   <si>
     <t>Cruz Ramos</t>
   </si>
   <si>
+    <t>icruzr1804@alumno.ipn.mx</t>
+  </si>
+  <si>
     <t>Itzel Alejandra</t>
   </si>
   <si>
     <t>Quintanar Arellano</t>
   </si>
   <si>
+    <t>itzel.quintanar@cinvestav.mx</t>
+  </si>
+  <si>
     <t>Ivan</t>
   </si>
   <si>
     <t>Alvarez Samario</t>
   </si>
   <si>
+    <t>ivan.alvarez@cinvestav.mx</t>
+  </si>
+  <si>
     <t>IVAN</t>
   </si>
   <si>
     <t>MORTERA BRAVO</t>
   </si>
   <si>
+    <t>imorbra@gmail.com</t>
+  </si>
+  <si>
     <t>Jael Arlen</t>
   </si>
   <si>
     <t>Briones Magallanes</t>
   </si>
   <si>
+    <t>jael.briones@cimav.edu.mx</t>
+  </si>
+  <si>
     <t>Jair Antonio</t>
   </si>
   <si>
     <t>Melchor Robles</t>
   </si>
   <si>
+    <t>jair.melchor@cinvestav.mx</t>
+  </si>
+  <si>
     <t>Jean Andree</t>
   </si>
   <si>
     <t>Morales Márquez</t>
   </si>
   <si>
+    <t>jeanandreemoralesmarquez@gmail.com</t>
+  </si>
+  <si>
     <t>Jessica Surisadai</t>
   </si>
   <si>
     <t>Rodríguez Aguilar</t>
   </si>
   <si>
+    <t>22jsuri@gmail.com</t>
+  </si>
+  <si>
     <t>Jesus abraham</t>
   </si>
   <si>
     <t>García Garcia</t>
   </si>
   <si>
+    <t>abrahamgarcia2568@gmail.com</t>
+  </si>
+  <si>
     <t>Jesús Dominguez</t>
   </si>
   <si>
     <t>Bravo</t>
   </si>
   <si>
+    <t>Jesus.dominguezbrav@gmail.com</t>
+  </si>
+  <si>
     <t>Jorge Alberto</t>
   </si>
   <si>
     <t>Flores Puon</t>
   </si>
   <si>
+    <t>nosey639@gmail.com</t>
+  </si>
+  <si>
     <t>Jorge Carlos</t>
   </si>
   <si>
     <t>Ávila Gaxiola</t>
   </si>
   <si>
+    <t>est.jorgeavila@uas.edu.mx</t>
+  </si>
+  <si>
     <t>Jorge Edgardo</t>
   </si>
   <si>
     <t>Martínez Salazar</t>
   </si>
   <si>
+    <t>jorgedomsalazar@gmail.com</t>
+  </si>
+  <si>
     <t>Jorge Luis</t>
   </si>
   <si>
     <t>Gutiérrez Santiago</t>
   </si>
   <si>
+    <t>jorge.gutierrez@cinvestav.mx</t>
+  </si>
+  <si>
     <t>Jorge Roberto</t>
   </si>
   <si>
     <t>Vargas García</t>
   </si>
   <si>
+    <t>rvargasga@ipn.mx</t>
+  </si>
+  <si>
     <t>Josafat Fracisco</t>
   </si>
   <si>
     <t>Zaragoza García</t>
   </si>
   <si>
+    <t>mosterrjoss10@gmail.com</t>
+  </si>
+  <si>
     <t>José</t>
   </si>
   <si>
     <t>Ledesma</t>
   </si>
   <si>
+    <t>Joseledesma7u7@gmail.com</t>
+  </si>
+  <si>
     <t>Reyes Osorio</t>
   </si>
   <si>
+    <t>jreyoso@gmail.com</t>
+  </si>
+  <si>
     <t>Jose Abraham</t>
   </si>
   <si>
     <t>Tellez Morales</t>
   </si>
   <si>
+    <t>abrahamtellez.morales@gmail.com</t>
+  </si>
+  <si>
     <t>José Alejandro</t>
   </si>
   <si>
     <t>Quiles Mendoza</t>
   </si>
   <si>
+    <t>quilesjosealejandro@gmail.com</t>
+  </si>
+  <si>
     <t>JOSE AMAURI</t>
   </si>
   <si>
     <t>SERRANO LAZARO</t>
   </si>
   <si>
+    <t>amauri.serrano@fisica.unam.mx</t>
+  </si>
+  <si>
     <t>José Antonio</t>
   </si>
   <si>
@@ -859,48 +1222,72 @@
     <t>Cruz Bueno</t>
   </si>
   <si>
+    <t>jc_bueno17@hotmail.com</t>
+  </si>
+  <si>
     <t>José Eduardo</t>
   </si>
   <si>
     <t>Santana Sánchez</t>
   </si>
   <si>
+    <t>jose.santana@teschic.edu.mx</t>
+  </si>
+  <si>
     <t>José Guadalupe</t>
   </si>
   <si>
     <t>Quiñones Galván</t>
   </si>
   <si>
+    <t>jose.quinones@academicos.udg.mx</t>
+  </si>
+  <si>
     <t>José Haziel</t>
   </si>
   <si>
     <t>González Moreno</t>
   </si>
   <si>
+    <t>jgonzalezm1803@alumno.ipn.mx</t>
+  </si>
+  <si>
     <t>José Humberto</t>
   </si>
   <si>
     <t>Parrilla de la O</t>
   </si>
   <si>
+    <t>jose.parrilla@cinvestav.mx</t>
+  </si>
+  <si>
     <t>José Juan</t>
   </si>
   <si>
     <t>Avilés Bravo</t>
   </si>
   <si>
+    <t>juan.aviles@inaoep.mx</t>
+  </si>
+  <si>
     <t>José Juan Jhonatan</t>
   </si>
   <si>
     <t>Diaz Lopez</t>
   </si>
   <si>
+    <t>Jose.diaz@cinvestav.mx</t>
+  </si>
+  <si>
     <t>José Luis</t>
   </si>
   <si>
     <t>Luna Sánchez</t>
   </si>
   <si>
+    <t>jluis.lunas@gmail.com</t>
+  </si>
+  <si>
     <t>Jiménez Pérez</t>
   </si>
   <si>
@@ -910,36 +1297,54 @@
     <t>Herrera Pérez</t>
   </si>
   <si>
+    <t>jherrerap@ipn.mx</t>
+  </si>
+  <si>
     <t>José Miguel</t>
   </si>
   <si>
     <t>Zárate Reyes</t>
   </si>
   <si>
+    <t>miguel.zarate@ciencias.unam.mx</t>
+  </si>
+  <si>
     <t>Jose Pablo</t>
   </si>
   <si>
     <t>Estrella Leyva</t>
   </si>
   <si>
+    <t>00estrellapablo@gmail.com</t>
+  </si>
+  <si>
     <t>José Pablo</t>
   </si>
   <si>
     <t>Ramírez Naranjo</t>
   </si>
   <si>
+    <t>jprn1991@gmail.com</t>
+  </si>
+  <si>
     <t>Josué Sain</t>
   </si>
   <si>
     <t>Romero Balderas</t>
   </si>
   <si>
+    <t>20191068@uatx.mx</t>
+  </si>
+  <si>
     <t>Juan Carlos</t>
   </si>
   <si>
     <t>Aguilar Márquez</t>
   </si>
   <si>
+    <t>20243896@uatx.mx</t>
+  </si>
+  <si>
     <t>Universidad Autonoma de Tlaxcala</t>
   </si>
   <si>
@@ -949,123 +1354,186 @@
     <t>Coronel De la cruz</t>
   </si>
   <si>
+    <t>juanp.cor.070511@gmail.com</t>
+  </si>
+  <si>
     <t>Judith</t>
   </si>
   <si>
     <t>Palma Rodarte</t>
   </si>
   <si>
+    <t>judith.palma@cinvestav.mx</t>
+  </si>
+  <si>
     <t>Julio Renzo Sebastian</t>
   </si>
   <si>
     <t>Zuñiga Pinillos</t>
   </si>
   <si>
+    <t>jzunigapi@unsa.edu.pe</t>
+  </si>
+  <si>
     <t>Jurgi</t>
   </si>
   <si>
     <t>Solari Feria</t>
   </si>
   <si>
+    <t>jurgisolari1@gmail.com</t>
+  </si>
+  <si>
     <t>Karen Aranzazu</t>
   </si>
   <si>
     <t>Vargas Robles</t>
   </si>
   <si>
+    <t>aranzarobles06@gmail.com</t>
+  </si>
+  <si>
     <t>Karen Olivia</t>
   </si>
   <si>
     <t>Martínez Clavería</t>
   </si>
   <si>
+    <t>Karen.oli.mtz@gmail.com</t>
+  </si>
+  <si>
     <t>Karina</t>
   </si>
   <si>
     <t>Cruz Martinez</t>
   </si>
   <si>
+    <t>karinacrzmz@gmail.com</t>
+  </si>
+  <si>
     <t>Portillo Cortez</t>
   </si>
   <si>
+    <t>portillo.ck90@gmail.com</t>
+  </si>
+  <si>
     <t>Karla Guadalupe</t>
   </si>
   <si>
     <t>Herrera Soriano</t>
   </si>
   <si>
+    <t>karlaherrera2250@gmail.com</t>
+  </si>
+  <si>
     <t>Karol Andrea</t>
   </si>
   <si>
     <t>Rodriguez Espinola</t>
   </si>
   <si>
+    <t>krodrigueze2200@alumno.ipn.mx</t>
+  </si>
+  <si>
     <t>Karol Valeria</t>
   </si>
   <si>
     <t>Guzman Gastelum</t>
   </si>
   <si>
+    <t>Valemandarinaaa@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Karolina </t>
   </si>
   <si>
     <t xml:space="preserve">Lira Gómez </t>
   </si>
   <si>
+    <t>vikaroli02@gmail.com</t>
+  </si>
+  <si>
     <t>Keila Regina</t>
   </si>
   <si>
     <t>Bohórquez Alcántara</t>
   </si>
   <si>
+    <t>Kbohorquezalcantara@gmail.com</t>
+  </si>
+  <si>
     <t>Kevin Enrique</t>
   </si>
   <si>
     <t>Salazar Martinez</t>
   </si>
   <si>
+    <t>mtzkevin700@gmail.com</t>
+  </si>
+  <si>
     <t>Kytzia</t>
   </si>
   <si>
     <t>Salazar Santana</t>
   </si>
   <si>
+    <t>kytzia.salazar.santana@upvm.edu.mx</t>
+  </si>
+  <si>
     <t>Laura</t>
   </si>
   <si>
     <t>Chavez castillo</t>
   </si>
   <si>
+    <t>lchllo1987@gmail.com</t>
+  </si>
+  <si>
     <t>Laura Goretty</t>
   </si>
   <si>
     <t>Rojas Rodriguez</t>
   </si>
   <si>
+    <t>gore_ro10@hotmail.com</t>
+  </si>
+  <si>
     <t>Laura Patricia</t>
   </si>
   <si>
     <t>Rivera Reséndiz</t>
   </si>
   <si>
+    <t>laura.rivera@academicos.udg.mx</t>
+  </si>
+  <si>
     <t>Leonardo Humberto</t>
   </si>
   <si>
     <t>Estevez Villegas</t>
   </si>
   <si>
+    <t>EsVLeonardo1501@gmail.com</t>
+  </si>
+  <si>
     <t>Leonardo Pablo</t>
   </si>
   <si>
     <t>Buendía Hernández</t>
   </si>
   <si>
+    <t>leonardobuendia1@gmail.com</t>
+  </si>
+  <si>
     <t>Lidia Paloma</t>
   </si>
   <si>
     <t>Torres Villafán</t>
   </si>
   <si>
+    <t>lidiapalomatv@gmail.com</t>
+  </si>
+  <si>
     <t>por</t>
   </si>
   <si>
@@ -1075,111 +1543,171 @@
     <t>Garay Cervantes</t>
   </si>
   <si>
+    <t>lilian.garay@cimav.edu.mx</t>
+  </si>
+  <si>
     <t>Lizbeth Aleida</t>
   </si>
   <si>
     <t>De la Cruz Pineda</t>
   </si>
   <si>
+    <t>3alizbethdelacruz@gmail.com</t>
+  </si>
+  <si>
     <t>Lizette Adriana</t>
   </si>
   <si>
     <t>Zebadúa Chavarría</t>
   </si>
   <si>
+    <t>lizette.zebadua@cinvestav.mx</t>
+  </si>
+  <si>
     <t>Luis Alberto</t>
   </si>
   <si>
     <t>Barajas Rodríguez</t>
   </si>
   <si>
+    <t>lbarajasr1101@alumno.ipn.mx</t>
+  </si>
+  <si>
+    <t>lalberto_hernandez@uaeh.edu.mx</t>
+  </si>
+  <si>
     <t>Luis Alejandro</t>
   </si>
   <si>
     <t>Cruz Benito</t>
   </si>
   <si>
+    <t>kotukocruz@gmail.com</t>
+  </si>
+  <si>
     <t>Luis Angel</t>
   </si>
   <si>
     <t>Absalon Garcia</t>
   </si>
   <si>
+    <t>absalongarciasluis@gmail.com</t>
+  </si>
+  <si>
     <t>Luis Antonio</t>
   </si>
   <si>
     <t>Sánchez Bautista</t>
   </si>
   <si>
+    <t>lsanchez20601@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Luis Martin </t>
   </si>
   <si>
     <t>Resendiz Mendoza</t>
   </si>
   <si>
+    <t>lresendiz@ipn.mx</t>
+  </si>
+  <si>
     <t>Luis Omar</t>
   </si>
   <si>
     <t>Sánchez Sánchez</t>
   </si>
   <si>
+    <t>sanchezluisomar@pceim.unam.mx</t>
+  </si>
+  <si>
     <t>Manolo</t>
   </si>
   <si>
     <t>Ramírez López</t>
   </si>
   <si>
+    <t>mrlopez.ipn@gmail.com</t>
+  </si>
+  <si>
     <t>Manuel</t>
   </si>
   <si>
     <t>Pérez Villegas</t>
   </si>
   <si>
+    <t>pv224570098@alm.buap.mx</t>
+  </si>
+  <si>
     <t>Manuel Airam</t>
   </si>
   <si>
     <t>Bernal López</t>
   </si>
   <si>
+    <t>Manuel.wbernal10@gmail.com</t>
+  </si>
+  <si>
     <t>Manuel Alejandro</t>
   </si>
   <si>
     <t>Martínez Morales</t>
   </si>
   <si>
+    <t>A01199614@tec.mx</t>
+  </si>
+  <si>
     <t>Mar</t>
   </si>
   <si>
     <t>Herrera Torres</t>
   </si>
   <si>
+    <t>21300530@uttt.edu.mx</t>
+  </si>
+  <si>
     <t>Marco Antonio</t>
   </si>
   <si>
     <t>Ramírez Orozco</t>
   </si>
   <si>
+    <t>marco.raor10@gmail.com</t>
+  </si>
+  <si>
     <t>Prado Reyes</t>
   </si>
   <si>
+    <t>mprador1500@alumno.ipn.mx</t>
+  </si>
+  <si>
     <t>Marco Favio</t>
   </si>
   <si>
     <t>De Paola Gallardo</t>
   </si>
   <si>
+    <t>dpaolafavio@outlook.com</t>
+  </si>
+  <si>
     <t>Marcos Miguel</t>
   </si>
   <si>
     <t>Atonal Ortega</t>
   </si>
   <si>
+    <t>atonal_mm2002@ciencias.unam.mx</t>
+  </si>
+  <si>
     <t>Margarita</t>
   </si>
   <si>
     <t>Barranco Tadeo</t>
   </si>
   <si>
+    <t>margaritatad@gmail.com</t>
+  </si>
+  <si>
     <t>Maria del</t>
   </si>
   <si>
@@ -1948,14 +2476,14 @@
     <t>email</t>
   </si>
   <si>
-    <t>edgaushome@gmail.com</t>
+    <t>msandovalc2102@alumno.ipn.mx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2092,13 +2620,6 @@
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
@@ -2448,11 +2969,10 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2829,7 +3349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35E6767-67BF-4C43-BB50-257DECA7AA9D}">
-  <dimension ref="A1:M266"/>
+  <dimension ref="A1:M1048572"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2849,7 +3369,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>641</v>
+        <v>817</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -2886,14 +3406,14 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>642</v>
+      <c r="D2" t="s">
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -2901,19 +3421,19 @@
         <v>46045.55</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>642</v>
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -2921,19 +3441,19 @@
         <v>46055.72152777778</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>642</v>
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -2944,19 +3464,19 @@
         <v>46045.674305555556</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>642</v>
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -2964,36 +3484,36 @@
         <v>46267.284722222219</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>642</v>
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>642</v>
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -3001,16 +3521,16 @@
         <v>46045.48541666667</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>642</v>
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -3018,19 +3538,19 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>642</v>
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -3041,19 +3561,19 @@
         <v>46046.48541666667</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>642</v>
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -3064,19 +3584,19 @@
         <v>46045.727777777778</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>642</v>
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -3087,19 +3607,19 @@
         <v>46046.727777777778</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>642</v>
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -3110,16 +3630,16 @@
         <v>46045.481249999997</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>642</v>
+        <v>56</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -3130,16 +3650,16 @@
         <v>46045.481944444444</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>642</v>
+        <v>59</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -3147,19 +3667,19 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>642</v>
+        <v>62</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -3167,19 +3687,19 @@
         <v>46045.51666666667</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>642</v>
+        <v>66</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="L16">
         <v>1</v>
@@ -3190,16 +3710,16 @@
         <v>46045.981249999997</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>642</v>
+        <v>70</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -3207,19 +3727,19 @@
         <v>46046.447916666664</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>642</v>
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -3230,16 +3750,16 @@
         <v>46056.543055555558</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>642</v>
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L19">
         <v>1</v>
@@ -3250,19 +3770,19 @@
         <v>46053.90625</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>642</v>
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="L20">
         <v>1</v>
@@ -3273,19 +3793,19 @@
         <v>46058.82916666667</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>642</v>
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -3296,19 +3816,19 @@
         <v>46268.375694444447</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>642</v>
+        <v>86</v>
+      </c>
+      <c r="D22" t="s">
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L22">
         <v>1</v>
@@ -3319,16 +3839,16 @@
         <v>46053.855555555558</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>642</v>
+        <v>89</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -3336,19 +3856,19 @@
         <v>46058.90902777778</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>642</v>
+        <v>92</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="L24">
         <v>1</v>
@@ -3359,19 +3879,19 @@
         <v>46056.462500000001</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>642</v>
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
+        <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -3379,19 +3899,19 @@
         <v>46061.008333333331</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>642</v>
+        <v>99</v>
+      </c>
+      <c r="D26" t="s">
+        <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -3399,16 +3919,16 @@
         <v>46045.481249999997</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>642</v>
+        <v>102</v>
+      </c>
+      <c r="D27" t="s">
+        <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L27">
         <v>1</v>
@@ -3419,19 +3939,19 @@
         <v>46058.623611111114</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>642</v>
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -3439,36 +3959,36 @@
         <v>46236.984027777777</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>642</v>
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>642</v>
+        <v>113</v>
+      </c>
+      <c r="D30" t="s">
+        <v>114</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -3476,16 +3996,16 @@
         <v>46053.932638888888</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>642</v>
+        <v>117</v>
+      </c>
+      <c r="D31" t="s">
+        <v>118</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -3493,19 +4013,19 @@
         <v>46061.009722222225</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>642</v>
+        <v>120</v>
+      </c>
+      <c r="D32" t="s">
+        <v>121</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L32">
         <v>1</v>
@@ -3516,19 +4036,19 @@
         <v>46047.7</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>642</v>
+        <v>123</v>
+      </c>
+      <c r="D33" t="s">
+        <v>124</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="L33">
         <v>1</v>
@@ -3539,19 +4059,19 @@
         <v>46058.683333333334</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>642</v>
+        <v>127</v>
+      </c>
+      <c r="D34" t="s">
+        <v>128</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="L34">
         <v>1</v>
@@ -3562,16 +4082,16 @@
         <v>46046.398611111108</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>642</v>
+        <v>131</v>
+      </c>
+      <c r="D35" t="s">
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L35">
         <v>1</v>
@@ -3582,16 +4102,16 @@
         <v>46053.84375</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>642</v>
+        <v>134</v>
+      </c>
+      <c r="D36" t="s">
+        <v>135</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -3602,16 +4122,16 @@
         <v>46054.723611111112</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>642</v>
+        <v>137</v>
+      </c>
+      <c r="D37" t="s">
+        <v>138</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L37">
         <v>1</v>
@@ -3622,30 +4142,30 @@
         <v>46058.645833333336</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>642</v>
+        <v>140</v>
+      </c>
+      <c r="D38" t="s">
+        <v>141</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>642</v>
+        <v>143</v>
+      </c>
+      <c r="D39" t="s">
+        <v>144</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L39">
         <v>1</v>
@@ -3656,16 +4176,16 @@
         <v>46045.477777777778</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>642</v>
+        <v>146</v>
+      </c>
+      <c r="D40" t="s">
+        <v>147</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L40">
         <v>1</v>
@@ -3676,16 +4196,16 @@
         <v>46056.531944444447</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="C41" t="s">
-        <v>110</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>642</v>
+        <v>149</v>
+      </c>
+      <c r="D41" t="s">
+        <v>150</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L41">
         <v>1</v>
@@ -3696,16 +4216,16 @@
         <v>46048.751388888886</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>642</v>
+        <v>152</v>
+      </c>
+      <c r="D42" t="s">
+        <v>153</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L42">
         <v>1</v>
@@ -3716,16 +4236,16 @@
         <v>46267.224999999999</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>642</v>
+        <v>155</v>
+      </c>
+      <c r="D43" t="s">
+        <v>156</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L43">
         <v>1</v>
@@ -3736,16 +4256,16 @@
         <v>46045.481249999997</v>
       </c>
       <c r="B44" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>642</v>
+        <v>158</v>
+      </c>
+      <c r="D44" t="s">
+        <v>159</v>
       </c>
       <c r="E44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L44">
         <v>1</v>
@@ -3756,16 +4276,16 @@
         <v>46061.975694444445</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="C45" t="s">
-        <v>117</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>642</v>
+        <v>160</v>
+      </c>
+      <c r="D45" t="s">
+        <v>161</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L45">
         <v>1</v>
@@ -3776,16 +4296,16 @@
         <v>46267.375694444447</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>642</v>
+        <v>158</v>
+      </c>
+      <c r="D46" t="s">
+        <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -3793,16 +4313,16 @@
         <v>46054.85</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="C47" t="s">
-        <v>119</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>642</v>
+        <v>163</v>
+      </c>
+      <c r="D47" t="s">
+        <v>164</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -3810,16 +4330,16 @@
         <v>46267.375694444447</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>642</v>
+        <v>163</v>
+      </c>
+      <c r="D48" t="s">
+        <v>164</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -3827,16 +4347,16 @@
         <v>46048.472222222219</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
-        <v>121</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>642</v>
+        <v>166</v>
+      </c>
+      <c r="D49" t="s">
+        <v>167</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -3844,16 +4364,16 @@
         <v>46053.932638888888</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>642</v>
+        <v>169</v>
+      </c>
+      <c r="D50" t="s">
+        <v>170</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L50">
         <v>1</v>
@@ -3864,16 +4384,16 @@
         <v>46046.425000000003</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="C51" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>642</v>
+        <v>172</v>
+      </c>
+      <c r="D51" t="s">
+        <v>173</v>
       </c>
       <c r="E51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L51">
         <v>1</v>
@@ -3884,16 +4404,16 @@
         <v>46045.482638888891</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>642</v>
+        <v>175</v>
+      </c>
+      <c r="D52" t="s">
+        <v>176</v>
       </c>
       <c r="E52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L52">
         <v>1</v>
@@ -3904,16 +4424,16 @@
         <v>46053.886805555558</v>
       </c>
       <c r="B53" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>642</v>
+        <v>178</v>
+      </c>
+      <c r="D53" t="s">
+        <v>179</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -3921,16 +4441,16 @@
         <v>46048.505555555559</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="C54" t="s">
-        <v>131</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>642</v>
+        <v>181</v>
+      </c>
+      <c r="D54" t="s">
+        <v>182</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L54">
         <v>1</v>
@@ -3941,16 +4461,16 @@
         <v>46058.695833333331</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="C55" t="s">
-        <v>132</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>642</v>
+        <v>183</v>
+      </c>
+      <c r="D55" t="s">
+        <v>184</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L55">
         <v>1</v>
@@ -3961,16 +4481,16 @@
         <v>46061.861805555556</v>
       </c>
       <c r="B56" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s">
-        <v>133</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>642</v>
+        <v>185</v>
+      </c>
+      <c r="D56" t="s">
+        <v>186</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -3981,16 +4501,16 @@
         <v>46053.8125</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>642</v>
+        <v>188</v>
+      </c>
+      <c r="D57" t="s">
+        <v>189</v>
       </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L57">
         <v>1</v>
@@ -4001,16 +4521,16 @@
         <v>46058.823611111111</v>
       </c>
       <c r="B58" t="s">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>642</v>
+        <v>190</v>
+      </c>
+      <c r="D58" t="s">
+        <v>191</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L58">
         <v>1</v>
@@ -4021,16 +4541,16 @@
         <v>46045.487500000003</v>
       </c>
       <c r="B59" t="s">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>642</v>
+        <v>193</v>
+      </c>
+      <c r="D59" t="s">
+        <v>194</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L59">
         <v>1</v>
@@ -4041,30 +4561,27 @@
         <v>46048.363888888889</v>
       </c>
       <c r="B60" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="C60" t="s">
-        <v>140</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>642</v>
+        <v>196</v>
+      </c>
+      <c r="D60" t="s">
+        <v>197</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="C61" t="s">
-        <v>142</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>642</v>
+        <v>199</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L61">
         <v>1</v>
@@ -4075,16 +4592,16 @@
         <v>46059.090277777781</v>
       </c>
       <c r="B62" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>642</v>
+        <v>201</v>
+      </c>
+      <c r="D62" t="s">
+        <v>202</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -4092,16 +4609,16 @@
         <v>46046.707638888889</v>
       </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="C63" t="s">
-        <v>146</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>642</v>
+        <v>204</v>
+      </c>
+      <c r="D63" t="s">
+        <v>205</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -4109,16 +4626,16 @@
         <v>46054.154166666667</v>
       </c>
       <c r="B64" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>642</v>
+        <v>207</v>
+      </c>
+      <c r="D64" t="s">
+        <v>208</v>
       </c>
       <c r="E64" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L64">
         <v>1</v>
@@ -4129,16 +4646,16 @@
         <v>46045.484027777777</v>
       </c>
       <c r="B65" t="s">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>642</v>
+        <v>210</v>
+      </c>
+      <c r="D65" t="s">
+        <v>211</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L65">
         <v>1</v>
@@ -4149,16 +4666,16 @@
         <v>46061.972916666666</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>212</v>
       </c>
       <c r="C66" t="s">
-        <v>152</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>642</v>
+        <v>213</v>
+      </c>
+      <c r="D66" t="s">
+        <v>214</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L66">
         <v>1</v>
@@ -4169,16 +4686,16 @@
         <v>46045.51458333333</v>
       </c>
       <c r="B67" t="s">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="C67" t="s">
-        <v>154</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>642</v>
+        <v>216</v>
+      </c>
+      <c r="D67" t="s">
+        <v>217</v>
       </c>
       <c r="E67" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -4186,16 +4703,16 @@
         <v>46060.899305555555</v>
       </c>
       <c r="B68" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="C68" t="s">
-        <v>156</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>642</v>
+        <v>219</v>
+      </c>
+      <c r="D68" t="s">
+        <v>220</v>
       </c>
       <c r="E68" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L68">
         <v>1</v>
@@ -4206,16 +4723,16 @@
         <v>46045.590277777781</v>
       </c>
       <c r="B69" t="s">
-        <v>157</v>
+        <v>221</v>
       </c>
       <c r="C69" t="s">
-        <v>158</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>642</v>
+        <v>222</v>
+      </c>
+      <c r="D69" t="s">
+        <v>223</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
@@ -4223,30 +4740,30 @@
         <v>46058.524305555555</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="C70" t="s">
-        <v>160</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>642</v>
+        <v>225</v>
+      </c>
+      <c r="D70" t="s">
+        <v>226</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="C71" t="s">
-        <v>162</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>642</v>
+        <v>228</v>
+      </c>
+      <c r="D71" t="s">
+        <v>229</v>
       </c>
       <c r="E71" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L71">
         <v>1</v>
@@ -4257,16 +4774,16 @@
         <v>46045.750694444447</v>
       </c>
       <c r="B72" t="s">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="C72" t="s">
-        <v>164</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>642</v>
+        <v>231</v>
+      </c>
+      <c r="D72" t="s">
+        <v>232</v>
       </c>
       <c r="E72" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -4274,16 +4791,16 @@
         <v>46058.859722222223</v>
       </c>
       <c r="B73" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="C73" t="s">
-        <v>166</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>642</v>
+        <v>234</v>
+      </c>
+      <c r="D73" t="s">
+        <v>235</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L73">
         <v>1</v>
@@ -4294,87 +4811,87 @@
         <v>46053.814583333333</v>
       </c>
       <c r="B74" t="s">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="C74" t="s">
-        <v>168</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>642</v>
+        <v>237</v>
+      </c>
+      <c r="D74" t="s">
+        <v>238</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <v>46045.5</v>
+        <v>46053.893055555556</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>239</v>
       </c>
       <c r="C75" t="s">
-        <v>170</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>642</v>
+        <v>240</v>
+      </c>
+      <c r="D75" t="s">
+        <v>241</v>
       </c>
       <c r="E75" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L75">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="1">
-        <v>46053.893055555556</v>
-      </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>642</v>
+        <v>243</v>
+      </c>
+      <c r="D76" t="s">
+        <v>244</v>
       </c>
       <c r="E76" t="s">
-        <v>19</v>
-      </c>
-      <c r="L76">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>46045.498611111114</v>
+      </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>245</v>
       </c>
       <c r="C77" t="s">
-        <v>174</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>642</v>
+        <v>246</v>
+      </c>
+      <c r="D77" t="s">
+        <v>247</v>
       </c>
       <c r="E77" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="L77">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <v>46045.498611111114</v>
+        <v>46058.416666666664</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="C78" t="s">
-        <v>176</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>642</v>
+        <v>249</v>
+      </c>
+      <c r="D78" t="s">
+        <v>250</v>
       </c>
       <c r="E78" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L78">
         <v>1</v>
@@ -4382,19 +4899,19 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <v>46058.416666666664</v>
+        <v>46058.524305555555</v>
       </c>
       <c r="B79" t="s">
-        <v>177</v>
+        <v>251</v>
       </c>
       <c r="C79" t="s">
-        <v>178</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>642</v>
+        <v>252</v>
+      </c>
+      <c r="D79" t="s">
+        <v>253</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L79">
         <v>1</v>
@@ -4402,73 +4919,73 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <v>46058.524305555555</v>
+        <v>46057.824305555558</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>254</v>
       </c>
       <c r="C80" t="s">
-        <v>180</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>642</v>
+        <v>255</v>
+      </c>
+      <c r="D80" t="s">
+        <v>256</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
-      </c>
-      <c r="L80">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <v>46057.824305555558</v>
+        <v>46045.477083333331</v>
       </c>
       <c r="B81" t="s">
-        <v>181</v>
+        <v>257</v>
       </c>
       <c r="C81" t="s">
-        <v>182</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>642</v>
+        <v>258</v>
+      </c>
+      <c r="D81" t="s">
+        <v>259</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
-        <v>46045.477083333331</v>
-      </c>
       <c r="B82" t="s">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>184</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="E82" t="s">
-        <v>13</v>
+        <v>261</v>
+      </c>
+      <c r="D82" t="s">
+        <v>262</v>
+      </c>
+      <c r="F82" t="s">
+        <v>68</v>
       </c>
       <c r="L82">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>46045.525000000001</v>
+      </c>
       <c r="B83" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="F83" t="s">
-        <v>53</v>
+        <v>264</v>
+      </c>
+      <c r="D83" t="s">
+        <v>265</v>
+      </c>
+      <c r="E83" t="s">
+        <v>22</v>
       </c>
       <c r="L83">
         <v>1</v>
@@ -4476,127 +4993,127 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
-        <v>46045.525000000001</v>
+        <v>46047.906944444447</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s">
-        <v>188</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>642</v>
+        <v>267</v>
+      </c>
+      <c r="D84" t="s">
+        <v>268</v>
       </c>
       <c r="E84" t="s">
-        <v>19</v>
-      </c>
-      <c r="L84">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
-        <v>46047.906944444447</v>
+        <v>46045.482638888891</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="C85" t="s">
-        <v>190</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>642</v>
+        <v>270</v>
+      </c>
+      <c r="D85" t="s">
+        <v>271</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
-        <v>46045.482638888891</v>
+        <v>46061.072916666664</v>
       </c>
       <c r="B86" t="s">
-        <v>191</v>
+        <v>272</v>
       </c>
       <c r="C86" t="s">
-        <v>192</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>642</v>
+        <v>273</v>
+      </c>
+      <c r="D86" t="s">
+        <v>274</v>
       </c>
       <c r="E86" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <v>46061.072916666664</v>
+        <v>46061.442361111112</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>275</v>
       </c>
       <c r="C87" t="s">
-        <v>194</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>642</v>
+        <v>181</v>
+      </c>
+      <c r="D87" t="s">
+        <v>276</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <v>46061.442361111112</v>
+        <v>46267.022222222222</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>277</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>642</v>
+        <v>278</v>
+      </c>
+      <c r="D88" t="s">
+        <v>279</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
-      </c>
-      <c r="L88">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <v>46267.022222222222</v>
+        <v>46053.87222222222</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
+        <v>280</v>
       </c>
       <c r="C89" t="s">
-        <v>197</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>642</v>
+        <v>281</v>
+      </c>
+      <c r="D89" t="s">
+        <v>282</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
-        <v>46053.87222222222</v>
+        <v>46271.375694444447</v>
       </c>
       <c r="B90" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="C90" t="s">
-        <v>199</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>642</v>
+        <v>284</v>
+      </c>
+      <c r="D90" t="s">
+        <v>285</v>
       </c>
       <c r="E90" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -4604,73 +5121,73 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <v>46271.375694444447</v>
+        <v>46045.477777777778</v>
       </c>
       <c r="B91" t="s">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="C91" t="s">
-        <v>201</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>642</v>
+        <v>287</v>
+      </c>
+      <c r="D91" t="s">
+        <v>288</v>
       </c>
       <c r="E91" t="s">
-        <v>13</v>
-      </c>
-      <c r="L91">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
-        <v>46045.477777777778</v>
+        <v>46045.486111111109</v>
       </c>
       <c r="B92" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="C92" t="s">
-        <v>203</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>642</v>
+        <v>290</v>
+      </c>
+      <c r="D92" t="s">
+        <v>291</v>
       </c>
       <c r="E92" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
-        <v>46045.486111111109</v>
+        <v>46059.474999999999</v>
       </c>
       <c r="B93" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="C93" t="s">
-        <v>205</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>642</v>
+        <v>293</v>
+      </c>
+      <c r="D93" t="s">
+        <v>294</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
-        <v>46059.474999999999</v>
+        <v>46061.685416666667</v>
       </c>
       <c r="B94" t="s">
-        <v>206</v>
+        <v>295</v>
       </c>
       <c r="C94" t="s">
-        <v>207</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>642</v>
+        <v>296</v>
+      </c>
+      <c r="D94" t="s">
+        <v>297</v>
       </c>
       <c r="E94" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L94">
         <v>1</v>
@@ -4678,283 +5195,283 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <v>46061.685416666667</v>
+        <v>46049.453472222223</v>
       </c>
       <c r="B95" t="s">
-        <v>208</v>
+        <v>298</v>
       </c>
       <c r="C95" t="s">
-        <v>209</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>642</v>
+        <v>299</v>
+      </c>
+      <c r="D95" t="s">
+        <v>300</v>
       </c>
       <c r="E95" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L95">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" s="1">
-        <v>46049.453472222223</v>
-      </c>
       <c r="B96" t="s">
-        <v>210</v>
-      </c>
-      <c r="C96" t="s">
-        <v>211</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>642</v>
+        <v>301</v>
+      </c>
+      <c r="D96" t="s">
+        <v>302</v>
       </c>
       <c r="E96" t="s">
-        <v>13</v>
-      </c>
-      <c r="L96">
-        <v>1</v>
+        <v>303</v>
+      </c>
+      <c r="F96" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>46054.569444444445</v>
+      </c>
       <c r="B97" t="s">
-        <v>212</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>642</v>
+        <v>305</v>
+      </c>
+      <c r="C97" t="s">
+        <v>306</v>
+      </c>
+      <c r="D97" t="s">
+        <v>307</v>
       </c>
       <c r="E97" t="s">
-        <v>213</v>
-      </c>
-      <c r="F97" t="s">
-        <v>214</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <v>46054.569444444445</v>
+        <v>46061.363888888889</v>
       </c>
       <c r="B98" t="s">
-        <v>215</v>
+        <v>308</v>
       </c>
       <c r="C98" t="s">
-        <v>216</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>642</v>
+        <v>309</v>
+      </c>
+      <c r="D98" t="s">
+        <v>310</v>
       </c>
       <c r="E98" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
-        <v>46061.363888888889</v>
-      </c>
       <c r="B99" t="s">
-        <v>217</v>
-      </c>
-      <c r="C99" t="s">
-        <v>218</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>642</v>
+        <v>311</v>
+      </c>
+      <c r="D99" t="s">
+        <v>312</v>
       </c>
       <c r="E99" t="s">
-        <v>13</v>
+        <v>303</v>
+      </c>
+      <c r="F99" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>46052.765277777777</v>
+      </c>
       <c r="B100" t="s">
-        <v>219</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>642</v>
+        <v>313</v>
+      </c>
+      <c r="C100" t="s">
+        <v>314</v>
+      </c>
+      <c r="D100" t="s">
+        <v>315</v>
       </c>
       <c r="E100" t="s">
-        <v>213</v>
-      </c>
-      <c r="F100" t="s">
-        <v>214</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <v>46052.765277777777</v>
+        <v>46052.348611111112</v>
       </c>
       <c r="B101" t="s">
-        <v>220</v>
+        <v>316</v>
       </c>
       <c r="C101" t="s">
-        <v>221</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>642</v>
+        <v>317</v>
+      </c>
+      <c r="D101" t="s">
+        <v>318</v>
       </c>
       <c r="E101" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
-        <v>46052.348611111112</v>
+        <v>46045.477083333331</v>
       </c>
       <c r="B102" t="s">
-        <v>222</v>
+        <v>319</v>
       </c>
       <c r="C102" t="s">
-        <v>223</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>642</v>
+        <v>320</v>
+      </c>
+      <c r="D102" t="s">
+        <v>321</v>
       </c>
       <c r="E102" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
-        <v>46045.477083333331</v>
+        <v>46058.405555555553</v>
       </c>
       <c r="B103" t="s">
-        <v>224</v>
+        <v>322</v>
       </c>
       <c r="C103" t="s">
-        <v>225</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>642</v>
+        <v>323</v>
+      </c>
+      <c r="D103" t="s">
+        <v>324</v>
       </c>
       <c r="E103" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
-        <v>46058.405555555553</v>
+        <v>46057.443749999999</v>
       </c>
       <c r="B104" t="s">
-        <v>226</v>
+        <v>325</v>
       </c>
       <c r="C104" t="s">
-        <v>227</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>642</v>
+        <v>326</v>
+      </c>
+      <c r="D104" t="s">
+        <v>327</v>
       </c>
       <c r="E104" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L104">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
-        <v>46057.443749999999</v>
-      </c>
       <c r="B105" t="s">
-        <v>228</v>
+        <v>328</v>
       </c>
       <c r="C105" t="s">
-        <v>229</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>642</v>
+        <v>329</v>
+      </c>
+      <c r="D105" t="s">
+        <v>330</v>
       </c>
       <c r="E105" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L105">
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>46045.520138888889</v>
+      </c>
       <c r="B106" t="s">
-        <v>230</v>
+        <v>331</v>
       </c>
       <c r="C106" t="s">
-        <v>231</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>642</v>
+        <v>332</v>
+      </c>
+      <c r="D106" t="s">
+        <v>333</v>
       </c>
       <c r="E106" t="s">
-        <v>13</v>
-      </c>
-      <c r="L106">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
-        <v>46045.520138888889</v>
+        <v>46045.540972222225</v>
       </c>
       <c r="B107" t="s">
-        <v>232</v>
+        <v>334</v>
       </c>
       <c r="C107" t="s">
-        <v>233</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>642</v>
+        <v>335</v>
+      </c>
+      <c r="D107" t="s">
+        <v>336</v>
       </c>
       <c r="E107" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
-        <v>46045.540972222225</v>
+        <v>46055.317361111112</v>
       </c>
       <c r="B108" t="s">
-        <v>234</v>
+        <v>337</v>
       </c>
       <c r="C108" t="s">
-        <v>235</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>642</v>
+        <v>338</v>
+      </c>
+      <c r="D108" t="s">
+        <v>339</v>
       </c>
       <c r="E108" t="s">
-        <v>19</v>
-      </c>
-      <c r="L108">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
-        <v>46055.317361111112</v>
+        <v>46045.548611111109</v>
       </c>
       <c r="B109" t="s">
-        <v>236</v>
+        <v>340</v>
       </c>
       <c r="C109" t="s">
-        <v>237</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>642</v>
+        <v>341</v>
+      </c>
+      <c r="D109" t="s">
+        <v>342</v>
       </c>
       <c r="E109" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
-        <v>46045.548611111109</v>
+        <v>46054.724999999999</v>
       </c>
       <c r="B110" t="s">
-        <v>238</v>
+        <v>343</v>
       </c>
       <c r="C110" t="s">
-        <v>239</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>642</v>
+        <v>344</v>
+      </c>
+      <c r="D110" t="s">
+        <v>345</v>
       </c>
       <c r="E110" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L110">
         <v>1</v>
@@ -4962,90 +5479,90 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
-        <v>46054.724999999999</v>
+        <v>46061.609027777777</v>
       </c>
       <c r="B111" t="s">
-        <v>240</v>
+        <v>340</v>
       </c>
       <c r="C111" t="s">
-        <v>241</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>642</v>
+        <v>341</v>
+      </c>
+      <c r="D111" t="s">
+        <v>342</v>
       </c>
       <c r="E111" t="s">
-        <v>19</v>
-      </c>
-      <c r="L111">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
-        <v>46061.609027777777</v>
+        <v>46053.814583333333</v>
       </c>
       <c r="B112" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="C112" t="s">
-        <v>239</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>642</v>
+        <v>347</v>
+      </c>
+      <c r="D112" t="s">
+        <v>348</v>
       </c>
       <c r="E112" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" s="1">
-        <v>46053.814583333333</v>
-      </c>
       <c r="B113" t="s">
-        <v>242</v>
+        <v>349</v>
       </c>
       <c r="C113" t="s">
-        <v>243</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>642</v>
+        <v>350</v>
+      </c>
+      <c r="D113" t="s">
+        <v>351</v>
       </c>
       <c r="E113" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="F113" t="s">
+        <v>129</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>244</v>
+        <v>352</v>
       </c>
       <c r="C114" t="s">
-        <v>245</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>642</v>
+        <v>353</v>
+      </c>
+      <c r="D114" t="s">
+        <v>354</v>
       </c>
       <c r="E114" t="s">
-        <v>19</v>
-      </c>
-      <c r="F114" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="L114">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>46045.481249999997</v>
+      </c>
       <c r="B115" t="s">
-        <v>246</v>
+        <v>355</v>
       </c>
       <c r="C115" t="s">
-        <v>247</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>642</v>
+        <v>356</v>
+      </c>
+      <c r="D115" t="s">
+        <v>357</v>
       </c>
       <c r="E115" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L115">
         <v>1</v>
@@ -5053,19 +5570,19 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
-        <v>46045.481249999997</v>
+        <v>46269.375694444447</v>
       </c>
       <c r="B116" t="s">
-        <v>248</v>
+        <v>358</v>
       </c>
       <c r="C116" t="s">
-        <v>249</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>642</v>
+        <v>359</v>
+      </c>
+      <c r="D116" t="s">
+        <v>360</v>
       </c>
       <c r="E116" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L116">
         <v>1</v>
@@ -5073,266 +5590,266 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
-        <v>46269.375694444447</v>
+        <v>46053.88958333333</v>
       </c>
       <c r="B117" t="s">
-        <v>250</v>
+        <v>361</v>
       </c>
       <c r="C117" t="s">
-        <v>251</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>642</v>
+        <v>362</v>
+      </c>
+      <c r="D117" t="s">
+        <v>363</v>
       </c>
       <c r="E117" t="s">
-        <v>13</v>
-      </c>
-      <c r="L117">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
-        <v>46053.88958333333</v>
+        <v>46046.333333333336</v>
       </c>
       <c r="B118" t="s">
-        <v>252</v>
+        <v>364</v>
       </c>
       <c r="C118" t="s">
-        <v>253</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>642</v>
+        <v>365</v>
+      </c>
+      <c r="D118" t="s">
+        <v>366</v>
       </c>
       <c r="E118" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
-        <v>46046.333333333336</v>
+        <v>46061.563888888886</v>
       </c>
       <c r="B119" t="s">
-        <v>254</v>
+        <v>367</v>
       </c>
       <c r="C119" t="s">
-        <v>255</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>642</v>
+        <v>368</v>
+      </c>
+      <c r="D119" t="s">
+        <v>369</v>
       </c>
       <c r="E119" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
-        <v>46061.563888888886</v>
+        <v>46058.525000000001</v>
       </c>
       <c r="B120" t="s">
-        <v>256</v>
+        <v>370</v>
       </c>
       <c r="C120" t="s">
-        <v>257</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>642</v>
+        <v>371</v>
+      </c>
+      <c r="D120" t="s">
+        <v>372</v>
       </c>
       <c r="E120" t="s">
-        <v>19</v>
-      </c>
-      <c r="L120">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
-        <v>46058.525000000001</v>
+        <v>46272.375694444447</v>
       </c>
       <c r="B121" t="s">
-        <v>258</v>
+        <v>373</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>642</v>
+        <v>374</v>
+      </c>
+      <c r="D121" t="s">
+        <v>375</v>
       </c>
       <c r="E121" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
-        <v>46272.375694444447</v>
+        <v>46045.810416666667</v>
       </c>
       <c r="B122" t="s">
-        <v>260</v>
+        <v>376</v>
       </c>
       <c r="C122" t="s">
-        <v>261</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>642</v>
+        <v>377</v>
+      </c>
+      <c r="D122" t="s">
+        <v>378</v>
       </c>
       <c r="E122" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
-        <v>46045.810416666667</v>
+        <v>46273.375694444447</v>
       </c>
       <c r="B123" t="s">
-        <v>262</v>
+        <v>379</v>
       </c>
       <c r="C123" t="s">
-        <v>263</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>642</v>
+        <v>380</v>
+      </c>
+      <c r="D123" t="s">
+        <v>381</v>
       </c>
       <c r="E123" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
-        <v>46273.375694444447</v>
+        <v>46053.8125</v>
       </c>
       <c r="B124" t="s">
-        <v>264</v>
+        <v>382</v>
       </c>
       <c r="C124" t="s">
-        <v>265</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>642</v>
+        <v>383</v>
+      </c>
+      <c r="D124" t="s">
+        <v>384</v>
       </c>
       <c r="E124" t="s">
-        <v>13</v>
-      </c>
-      <c r="L124">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A125" s="1">
-        <v>46053.8125</v>
-      </c>
       <c r="B125" t="s">
-        <v>266</v>
+        <v>382</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>642</v>
+        <v>385</v>
+      </c>
+      <c r="D125" t="s">
+        <v>386</v>
       </c>
       <c r="E125" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>46057.667361111111</v>
+      </c>
       <c r="B126" t="s">
-        <v>266</v>
+        <v>387</v>
       </c>
       <c r="C126" t="s">
-        <v>268</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>642</v>
+        <v>388</v>
+      </c>
+      <c r="D126" t="s">
+        <v>389</v>
       </c>
       <c r="E126" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
-        <v>46057.667361111111</v>
+        <v>46275.375694444447</v>
       </c>
       <c r="B127" t="s">
-        <v>269</v>
+        <v>390</v>
       </c>
       <c r="C127" t="s">
-        <v>270</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>642</v>
+        <v>391</v>
+      </c>
+      <c r="D127" t="s">
+        <v>392</v>
       </c>
       <c r="E127" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
-        <v>46275.375694444447</v>
+        <v>46061.979166666664</v>
       </c>
       <c r="B128" t="s">
-        <v>271</v>
+        <v>393</v>
       </c>
       <c r="C128" t="s">
-        <v>272</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>642</v>
+        <v>394</v>
+      </c>
+      <c r="D128" t="s">
+        <v>395</v>
       </c>
       <c r="E128" t="s">
-        <v>13</v>
-      </c>
-      <c r="L128">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
-        <v>46061.979166666664</v>
+        <v>46045.479166666664</v>
       </c>
       <c r="B129" t="s">
-        <v>273</v>
+        <v>396</v>
       </c>
       <c r="C129" t="s">
-        <v>274</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>642</v>
+        <v>397</v>
+      </c>
+      <c r="D129" t="s">
+        <v>384</v>
       </c>
       <c r="E129" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
-        <v>46045.479166666664</v>
+        <v>46048.508333333331</v>
       </c>
       <c r="B130" t="s">
-        <v>275</v>
+        <v>398</v>
       </c>
       <c r="C130" t="s">
-        <v>276</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>642</v>
+        <v>399</v>
+      </c>
+      <c r="D130" t="s">
+        <v>400</v>
       </c>
       <c r="E130" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
-        <v>46048.508333333331</v>
+        <v>46058.782638888886</v>
       </c>
       <c r="B131" t="s">
-        <v>277</v>
+        <v>401</v>
       </c>
       <c r="C131" t="s">
-        <v>278</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>642</v>
+        <v>402</v>
+      </c>
+      <c r="D131" t="s">
+        <v>403</v>
       </c>
       <c r="E131" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -5340,56 +5857,56 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
-        <v>46058.782638888886</v>
+        <v>46061.915972222225</v>
       </c>
       <c r="B132" t="s">
-        <v>279</v>
+        <v>404</v>
       </c>
       <c r="C132" t="s">
-        <v>280</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>642</v>
+        <v>405</v>
+      </c>
+      <c r="D132" t="s">
+        <v>406</v>
       </c>
       <c r="E132" t="s">
-        <v>13</v>
-      </c>
-      <c r="L132">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
-        <v>46061.915972222225</v>
+        <v>46058.586805555555</v>
       </c>
       <c r="B133" t="s">
-        <v>281</v>
+        <v>407</v>
       </c>
       <c r="C133" t="s">
-        <v>282</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>642</v>
+        <v>408</v>
+      </c>
+      <c r="D133" t="s">
+        <v>409</v>
       </c>
       <c r="E133" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
-        <v>46058.586805555555</v>
+        <v>46054.70416666667</v>
       </c>
       <c r="B134" t="s">
-        <v>283</v>
+        <v>410</v>
       </c>
       <c r="C134" t="s">
-        <v>284</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>642</v>
+        <v>411</v>
+      </c>
+      <c r="D134" t="s">
+        <v>412</v>
       </c>
       <c r="E134" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L134">
         <v>1</v>
@@ -5397,19 +5914,19 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
-        <v>46054.70416666667</v>
+        <v>46056.484027777777</v>
       </c>
       <c r="B135" t="s">
-        <v>285</v>
+        <v>413</v>
       </c>
       <c r="C135" t="s">
-        <v>286</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>642</v>
+        <v>414</v>
+      </c>
+      <c r="D135" t="s">
+        <v>415</v>
       </c>
       <c r="E135" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L135">
         <v>1</v>
@@ -5417,56 +5934,50 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
-        <v>46056.484027777777</v>
+        <v>46045.490972222222</v>
       </c>
       <c r="B136" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
       <c r="C136" t="s">
-        <v>288</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>642</v>
+        <v>417</v>
+      </c>
+      <c r="D136" t="s">
+        <v>418</v>
       </c>
       <c r="E136" t="s">
-        <v>19</v>
-      </c>
-      <c r="L136">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
-        <v>46045.490972222222</v>
+        <v>46045.760416666664</v>
       </c>
       <c r="B137" t="s">
-        <v>289</v>
+        <v>419</v>
       </c>
       <c r="C137" t="s">
-        <v>290</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>642</v>
+        <v>420</v>
+      </c>
+      <c r="D137" t="s">
+        <v>421</v>
       </c>
       <c r="E137" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
-        <v>46045.760416666664</v>
-      </c>
       <c r="B138" t="s">
-        <v>291</v>
+        <v>419</v>
       </c>
       <c r="C138" t="s">
-        <v>292</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>642</v>
+        <v>422</v>
       </c>
       <c r="E138" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L138">
         <v>1</v>
@@ -5474,33 +5985,36 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
-        <v>291</v>
+        <v>423</v>
       </c>
       <c r="C139" t="s">
-        <v>293</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>642</v>
+        <v>424</v>
+      </c>
+      <c r="D139" t="s">
+        <v>425</v>
       </c>
       <c r="E139" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L139">
         <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>46058.65347222222</v>
+      </c>
       <c r="B140" t="s">
-        <v>294</v>
+        <v>426</v>
       </c>
       <c r="C140" t="s">
-        <v>295</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>642</v>
+        <v>427</v>
+      </c>
+      <c r="D140" t="s">
+        <v>428</v>
       </c>
       <c r="E140" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L140">
         <v>1</v>
@@ -5508,73 +6022,76 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
-        <v>46058.65347222222</v>
+        <v>46057.720833333333</v>
       </c>
       <c r="B141" t="s">
-        <v>296</v>
+        <v>429</v>
       </c>
       <c r="C141" t="s">
-        <v>297</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>642</v>
+        <v>430</v>
+      </c>
+      <c r="D141" t="s">
+        <v>431</v>
       </c>
       <c r="E141" t="s">
-        <v>19</v>
-      </c>
-      <c r="L141">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
-        <v>46057.720833333333</v>
+        <v>46045.477083333331</v>
       </c>
       <c r="B142" t="s">
-        <v>298</v>
+        <v>432</v>
       </c>
       <c r="C142" t="s">
-        <v>299</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>642</v>
+        <v>433</v>
+      </c>
+      <c r="D142" t="s">
+        <v>434</v>
       </c>
       <c r="E142" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
-        <v>46045.477083333331</v>
+        <v>46050.434027777781</v>
       </c>
       <c r="B143" t="s">
-        <v>300</v>
+        <v>435</v>
       </c>
       <c r="C143" t="s">
-        <v>301</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>642</v>
+        <v>436</v>
+      </c>
+      <c r="D143" t="s">
+        <v>437</v>
       </c>
       <c r="E143" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
-        <v>46050.434027777781</v>
+        <v>46053.90347222222</v>
       </c>
       <c r="B144" t="s">
-        <v>302</v>
+        <v>438</v>
       </c>
       <c r="C144" t="s">
-        <v>303</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>642</v>
+        <v>439</v>
+      </c>
+      <c r="D144" t="s">
+        <v>440</v>
       </c>
       <c r="E144" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="F144" t="s">
+        <v>441</v>
       </c>
       <c r="L144">
         <v>1</v>
@@ -5582,22 +6099,19 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
-        <v>46053.90347222222</v>
+        <v>46060.9</v>
       </c>
       <c r="B145" t="s">
-        <v>304</v>
+        <v>442</v>
       </c>
       <c r="C145" t="s">
-        <v>305</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>642</v>
+        <v>443</v>
+      </c>
+      <c r="D145" t="s">
+        <v>444</v>
       </c>
       <c r="E145" t="s">
-        <v>19</v>
-      </c>
-      <c r="F145" t="s">
-        <v>306</v>
+        <v>14</v>
       </c>
       <c r="L145">
         <v>1</v>
@@ -5605,19 +6119,19 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
-        <v>46060.9</v>
+        <v>46054.001388888886</v>
       </c>
       <c r="B146" t="s">
-        <v>307</v>
+        <v>445</v>
       </c>
       <c r="C146" t="s">
-        <v>308</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>642</v>
+        <v>446</v>
+      </c>
+      <c r="D146" t="s">
+        <v>447</v>
       </c>
       <c r="E146" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L146">
         <v>1</v>
@@ -5625,110 +6139,110 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
-        <v>46054.001388888886</v>
+        <v>46061.070833333331</v>
       </c>
       <c r="B147" t="s">
-        <v>309</v>
+        <v>448</v>
       </c>
       <c r="C147" t="s">
-        <v>310</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>642</v>
+        <v>449</v>
+      </c>
+      <c r="D147" t="s">
+        <v>450</v>
       </c>
       <c r="E147" t="s">
-        <v>13</v>
-      </c>
-      <c r="L147">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
-        <v>46061.070833333331</v>
+        <v>46059.894444444442</v>
       </c>
       <c r="B148" t="s">
-        <v>311</v>
+        <v>451</v>
       </c>
       <c r="C148" t="s">
-        <v>312</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>642</v>
+        <v>452</v>
+      </c>
+      <c r="D148" t="s">
+        <v>453</v>
       </c>
       <c r="E148" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
-        <v>46059.894444444442</v>
+        <v>46058.52847222222</v>
       </c>
       <c r="B149" t="s">
-        <v>313</v>
+        <v>454</v>
       </c>
       <c r="C149" t="s">
-        <v>314</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>642</v>
+        <v>455</v>
+      </c>
+      <c r="D149" t="s">
+        <v>456</v>
       </c>
       <c r="E149" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L149">
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
-        <v>46058.52847222222</v>
+        <v>46057.681944444441</v>
       </c>
       <c r="B150" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="C150" t="s">
-        <v>316</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>642</v>
+        <v>458</v>
+      </c>
+      <c r="D150" t="s">
+        <v>459</v>
       </c>
       <c r="E150" t="s">
-        <v>13</v>
-      </c>
-      <c r="L150">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
-        <v>46057.681944444441</v>
+        <v>46050.825694444444</v>
       </c>
       <c r="B151" t="s">
-        <v>317</v>
+        <v>460</v>
       </c>
       <c r="C151" t="s">
-        <v>318</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>642</v>
+        <v>461</v>
+      </c>
+      <c r="D151" t="s">
+        <v>462</v>
       </c>
       <c r="E151" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L151">
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
-        <v>46050.825694444444</v>
+        <v>46058.631249999999</v>
       </c>
       <c r="B152" t="s">
-        <v>319</v>
+        <v>460</v>
       </c>
       <c r="C152" t="s">
-        <v>320</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>642</v>
+        <v>463</v>
+      </c>
+      <c r="D152" t="s">
+        <v>464</v>
       </c>
       <c r="E152" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L152">
         <v>1</v>
@@ -5736,90 +6250,90 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
-        <v>46058.631249999999</v>
+        <v>46046.84652777778</v>
       </c>
       <c r="B153" t="s">
-        <v>319</v>
+        <v>465</v>
       </c>
       <c r="C153" t="s">
-        <v>321</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>642</v>
+        <v>466</v>
+      </c>
+      <c r="D153" t="s">
+        <v>467</v>
       </c>
       <c r="E153" t="s">
-        <v>19</v>
-      </c>
-      <c r="L153">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
-        <v>46046.84652777778</v>
+        <v>46045.665277777778</v>
       </c>
       <c r="B154" t="s">
-        <v>322</v>
+        <v>468</v>
       </c>
       <c r="C154" t="s">
-        <v>323</v>
-      </c>
-      <c r="D154" s="3" t="s">
-        <v>642</v>
+        <v>469</v>
+      </c>
+      <c r="D154" t="s">
+        <v>470</v>
       </c>
       <c r="E154" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
-        <v>46045.665277777778</v>
+        <v>46061.665277777778</v>
       </c>
       <c r="B155" t="s">
-        <v>324</v>
+        <v>471</v>
       </c>
       <c r="C155" t="s">
-        <v>325</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>642</v>
+        <v>472</v>
+      </c>
+      <c r="D155" t="s">
+        <v>473</v>
       </c>
       <c r="E155" t="s">
-        <v>13</v>
-      </c>
-      <c r="L155">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A156" s="1">
-        <v>46061.665277777778</v>
-      </c>
       <c r="B156" t="s">
-        <v>326</v>
+        <v>474</v>
       </c>
       <c r="C156" t="s">
-        <v>327</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>642</v>
+        <v>475</v>
+      </c>
+      <c r="D156" t="s">
+        <v>476</v>
       </c>
       <c r="E156" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>46060.944444444445</v>
+      </c>
       <c r="B157" t="s">
-        <v>328</v>
+        <v>477</v>
       </c>
       <c r="C157" t="s">
-        <v>329</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>642</v>
+        <v>478</v>
+      </c>
+      <c r="D157" t="s">
+        <v>479</v>
       </c>
       <c r="E157" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L157">
         <v>1</v>
@@ -5827,19 +6341,19 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
-        <v>46060.944444444445</v>
+        <v>46053.925694444442</v>
       </c>
       <c r="B158" t="s">
-        <v>330</v>
+        <v>480</v>
       </c>
       <c r="C158" t="s">
-        <v>331</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>642</v>
+        <v>481</v>
+      </c>
+      <c r="D158" t="s">
+        <v>482</v>
       </c>
       <c r="E158" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L158">
         <v>1</v>
@@ -5847,73 +6361,73 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
-        <v>46053.925694444442</v>
+        <v>46049.59097222222</v>
       </c>
       <c r="B159" t="s">
-        <v>332</v>
+        <v>483</v>
       </c>
       <c r="C159" t="s">
-        <v>333</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>642</v>
+        <v>484</v>
+      </c>
+      <c r="D159" t="s">
+        <v>485</v>
       </c>
       <c r="E159" t="s">
-        <v>13</v>
-      </c>
-      <c r="L159">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
-        <v>46049.59097222222</v>
+        <v>46058.714583333334</v>
       </c>
       <c r="B160" t="s">
-        <v>334</v>
+        <v>486</v>
       </c>
       <c r="C160" t="s">
-        <v>335</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>642</v>
+        <v>487</v>
+      </c>
+      <c r="D160" t="s">
+        <v>488</v>
       </c>
       <c r="E160" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="L160">
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A161" s="1">
-        <v>46058.714583333334</v>
-      </c>
       <c r="B161" t="s">
-        <v>336</v>
+        <v>489</v>
       </c>
       <c r="C161" t="s">
-        <v>337</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>642</v>
+        <v>490</v>
+      </c>
+      <c r="D161" t="s">
+        <v>491</v>
       </c>
       <c r="E161" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L161">
         <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>46061.913888888892</v>
+      </c>
       <c r="B162" t="s">
-        <v>338</v>
+        <v>492</v>
       </c>
       <c r="C162" t="s">
-        <v>339</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>642</v>
+        <v>493</v>
+      </c>
+      <c r="D162" t="s">
+        <v>494</v>
       </c>
       <c r="E162" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L162">
         <v>1</v>
@@ -5921,141 +6435,141 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
-        <v>46061.913888888892</v>
+        <v>46054.587500000001</v>
       </c>
       <c r="B163" t="s">
-        <v>340</v>
+        <v>495</v>
       </c>
       <c r="C163" t="s">
-        <v>341</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>642</v>
+        <v>496</v>
+      </c>
+      <c r="D163" t="s">
+        <v>497</v>
       </c>
       <c r="E163" t="s">
-        <v>19</v>
-      </c>
-      <c r="L163">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A164" s="1">
-        <v>46054.587500000001</v>
-      </c>
       <c r="B164" t="s">
-        <v>342</v>
+        <v>498</v>
       </c>
       <c r="C164" t="s">
-        <v>343</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>642</v>
+        <v>499</v>
+      </c>
+      <c r="D164" t="s">
+        <v>500</v>
       </c>
       <c r="E164" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
-        <v>344</v>
+        <v>501</v>
       </c>
       <c r="C165" t="s">
-        <v>345</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>642</v>
+        <v>502</v>
+      </c>
+      <c r="D165" t="s">
+        <v>503</v>
       </c>
       <c r="E165" t="s">
-        <v>13</v>
-      </c>
-      <c r="L165">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="G165" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>46267.45</v>
+      </c>
       <c r="B166" t="s">
-        <v>346</v>
+        <v>501</v>
       </c>
       <c r="C166" t="s">
-        <v>347</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>642</v>
+        <v>502</v>
+      </c>
+      <c r="D166" t="s">
+        <v>503</v>
       </c>
       <c r="E166" t="s">
-        <v>19</v>
-      </c>
-      <c r="G166" t="s">
-        <v>348</v>
+        <v>22</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
-        <v>46267.45</v>
+        <v>46054.402777777781</v>
       </c>
       <c r="B167" t="s">
-        <v>346</v>
+        <v>505</v>
       </c>
       <c r="C167" t="s">
-        <v>347</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>642</v>
+        <v>506</v>
+      </c>
+      <c r="D167" t="s">
+        <v>507</v>
       </c>
       <c r="E167" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
-        <v>46054.402777777781</v>
+        <v>46058.525000000001</v>
       </c>
       <c r="B168" t="s">
-        <v>349</v>
+        <v>508</v>
       </c>
       <c r="C168" t="s">
-        <v>350</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>642</v>
+        <v>509</v>
+      </c>
+      <c r="D168" t="s">
+        <v>510</v>
       </c>
       <c r="E168" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
-        <v>46058.525000000001</v>
+        <v>46045.490972222222</v>
       </c>
       <c r="B169" t="s">
-        <v>351</v>
+        <v>511</v>
       </c>
       <c r="C169" t="s">
-        <v>352</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>642</v>
+        <v>512</v>
+      </c>
+      <c r="D169" t="s">
+        <v>513</v>
       </c>
       <c r="E169" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
-        <v>46045.490972222222</v>
+        <v>46047.944444444445</v>
       </c>
       <c r="B170" t="s">
-        <v>353</v>
+        <v>514</v>
       </c>
       <c r="C170" t="s">
-        <v>354</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>642</v>
+        <v>515</v>
+      </c>
+      <c r="D170" t="s">
+        <v>516</v>
       </c>
       <c r="E170" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L170">
         <v>1</v>
@@ -6063,104 +6577,104 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
-        <v>46047.944444444445</v>
+        <v>46049.425694444442</v>
       </c>
       <c r="B171" t="s">
-        <v>355</v>
+        <v>514</v>
       </c>
       <c r="C171" t="s">
-        <v>356</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>642</v>
+        <v>102</v>
+      </c>
+      <c r="D171" t="s">
+        <v>517</v>
       </c>
       <c r="E171" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L171">
         <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A172" s="1">
-        <v>46049.425694444442</v>
-      </c>
       <c r="B172" t="s">
-        <v>355</v>
+        <v>518</v>
       </c>
       <c r="C172" t="s">
-        <v>77</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>642</v>
+        <v>519</v>
+      </c>
+      <c r="D172" t="s">
+        <v>520</v>
       </c>
       <c r="E172" t="s">
-        <v>19</v>
-      </c>
-      <c r="L172">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>46061.645138888889</v>
+      </c>
       <c r="B173" t="s">
-        <v>357</v>
+        <v>521</v>
       </c>
       <c r="C173" t="s">
-        <v>358</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>642</v>
+        <v>522</v>
+      </c>
+      <c r="D173" t="s">
+        <v>523</v>
       </c>
       <c r="E173" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
-        <v>46061.645138888889</v>
+        <v>46045.509722222225</v>
       </c>
       <c r="B174" t="s">
-        <v>359</v>
+        <v>524</v>
       </c>
       <c r="C174" t="s">
-        <v>360</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>642</v>
+        <v>525</v>
+      </c>
+      <c r="D174" t="s">
+        <v>526</v>
       </c>
       <c r="E174" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A175" s="1">
-        <v>46045.509722222225</v>
-      </c>
       <c r="B175" t="s">
-        <v>361</v>
+        <v>527</v>
       </c>
       <c r="C175" t="s">
-        <v>362</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>642</v>
+        <v>528</v>
+      </c>
+      <c r="D175" t="s">
+        <v>529</v>
       </c>
       <c r="E175" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>46061.477777777778</v>
+      </c>
       <c r="B176" t="s">
-        <v>363</v>
+        <v>530</v>
       </c>
       <c r="C176" t="s">
-        <v>364</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>642</v>
+        <v>531</v>
+      </c>
+      <c r="D176" t="s">
+        <v>532</v>
       </c>
       <c r="E176" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L176">
         <v>1</v>
@@ -6168,19 +6682,19 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
-        <v>46061.477777777778</v>
+        <v>46045.495138888888</v>
       </c>
       <c r="B177" t="s">
-        <v>365</v>
+        <v>533</v>
       </c>
       <c r="C177" t="s">
-        <v>366</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>642</v>
+        <v>534</v>
+      </c>
+      <c r="D177" t="s">
+        <v>535</v>
       </c>
       <c r="E177" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -6188,19 +6702,19 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
-        <v>46045.495138888888</v>
+        <v>46058.535416666666</v>
       </c>
       <c r="B178" t="s">
-        <v>367</v>
+        <v>536</v>
       </c>
       <c r="C178" t="s">
-        <v>368</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>642</v>
+        <v>537</v>
+      </c>
+      <c r="D178" t="s">
+        <v>538</v>
       </c>
       <c r="E178" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L178">
         <v>1</v>
@@ -6208,346 +6722,346 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
-        <v>46058.535416666666</v>
+        <v>46045.53402777778</v>
       </c>
       <c r="B179" t="s">
-        <v>369</v>
+        <v>539</v>
       </c>
       <c r="C179" t="s">
-        <v>370</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>642</v>
+        <v>540</v>
+      </c>
+      <c r="D179" t="s">
+        <v>541</v>
       </c>
       <c r="E179" t="s">
-        <v>19</v>
-      </c>
-      <c r="L179">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
-        <v>46045.53402777778</v>
+        <v>46057.427777777775</v>
       </c>
       <c r="B180" t="s">
-        <v>371</v>
+        <v>542</v>
       </c>
       <c r="C180" t="s">
-        <v>372</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>642</v>
+        <v>543</v>
+      </c>
+      <c r="D180" t="s">
+        <v>544</v>
       </c>
       <c r="E180" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
-        <v>46057.427777777775</v>
+        <v>46054.956250000003</v>
       </c>
       <c r="B181" t="s">
-        <v>373</v>
+        <v>545</v>
       </c>
       <c r="C181" t="s">
-        <v>374</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>642</v>
+        <v>546</v>
+      </c>
+      <c r="D181" t="s">
+        <v>547</v>
       </c>
       <c r="E181" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
-        <v>46054.956250000003</v>
+        <v>46045.482638888891</v>
       </c>
       <c r="B182" t="s">
-        <v>375</v>
+        <v>548</v>
       </c>
       <c r="C182" t="s">
-        <v>376</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>642</v>
+        <v>549</v>
+      </c>
+      <c r="D182" t="s">
+        <v>550</v>
       </c>
       <c r="E182" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
-        <v>46045.482638888891</v>
+        <v>46047.510416666664</v>
       </c>
       <c r="B183" t="s">
-        <v>377</v>
+        <v>548</v>
       </c>
       <c r="C183" t="s">
-        <v>378</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>642</v>
+        <v>551</v>
+      </c>
+      <c r="D183" t="s">
+        <v>552</v>
       </c>
       <c r="E183" t="s">
-        <v>13</v>
-      </c>
-      <c r="L183">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
-        <v>46047.510416666664</v>
+        <v>46048.482638888891</v>
       </c>
       <c r="B184" t="s">
-        <v>377</v>
+        <v>553</v>
       </c>
       <c r="C184" t="s">
-        <v>379</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>642</v>
+        <v>554</v>
+      </c>
+      <c r="D184" t="s">
+        <v>555</v>
       </c>
       <c r="E184" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
-        <v>46048.482638888891</v>
+        <v>46053.886111111111</v>
       </c>
       <c r="B185" t="s">
-        <v>380</v>
+        <v>556</v>
       </c>
       <c r="C185" t="s">
-        <v>381</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>642</v>
+        <v>557</v>
+      </c>
+      <c r="D185" t="s">
+        <v>558</v>
       </c>
       <c r="E185" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
-        <v>46053.886111111111</v>
+        <v>46061.354166666664</v>
       </c>
       <c r="B186" t="s">
-        <v>382</v>
+        <v>559</v>
       </c>
       <c r="C186" t="s">
-        <v>383</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>642</v>
+        <v>560</v>
+      </c>
+      <c r="D186" t="s">
+        <v>561</v>
       </c>
       <c r="E186" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
-        <v>46061.354166666664</v>
+        <v>46053.816666666666</v>
       </c>
       <c r="B187" t="s">
-        <v>384</v>
+        <v>562</v>
       </c>
       <c r="C187" t="s">
-        <v>385</v>
+        <v>563</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>642</v>
+        <v>818</v>
       </c>
       <c r="E187" t="s">
-        <v>19</v>
-      </c>
-      <c r="L187">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="F187" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
-        <v>46053.816666666666</v>
+        <v>46053.947916666664</v>
       </c>
       <c r="B188" t="s">
-        <v>386</v>
+        <v>565</v>
       </c>
       <c r="C188" t="s">
-        <v>387</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>642</v>
+        <v>566</v>
+      </c>
+      <c r="D188" t="s">
+        <v>567</v>
       </c>
       <c r="E188" t="s">
-        <v>19</v>
-      </c>
-      <c r="F188" t="s">
-        <v>388</v>
+        <v>22</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
-        <v>46053.947916666664</v>
+        <v>46061.054861111108</v>
       </c>
       <c r="B189" t="s">
-        <v>389</v>
+        <v>568</v>
       </c>
       <c r="C189" t="s">
-        <v>390</v>
+        <v>569</v>
       </c>
       <c r="D189" t="s">
-        <v>391</v>
+        <v>570</v>
       </c>
       <c r="E189" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
-        <v>46061.054861111108</v>
+        <v>46058.520833333336</v>
       </c>
       <c r="B190" t="s">
-        <v>392</v>
+        <v>571</v>
       </c>
       <c r="C190" t="s">
-        <v>393</v>
+        <v>572</v>
       </c>
       <c r="D190" t="s">
-        <v>394</v>
+        <v>573</v>
       </c>
       <c r="E190" t="s">
-        <v>13</v>
-      </c>
-      <c r="L190">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
-        <v>46058.520833333336</v>
+        <v>46058.537499999999</v>
       </c>
       <c r="B191" t="s">
-        <v>395</v>
+        <v>574</v>
       </c>
       <c r="C191" t="s">
-        <v>396</v>
+        <v>575</v>
       </c>
       <c r="D191" t="s">
-        <v>397</v>
+        <v>576</v>
       </c>
       <c r="E191" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L191">
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
-        <v>46058.537499999999</v>
+        <v>46046.049305555556</v>
       </c>
       <c r="B192" t="s">
-        <v>398</v>
+        <v>577</v>
       </c>
       <c r="C192" t="s">
-        <v>399</v>
+        <v>578</v>
       </c>
       <c r="D192" t="s">
-        <v>400</v>
+        <v>579</v>
       </c>
       <c r="E192" t="s">
-        <v>13</v>
-      </c>
-      <c r="L192">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
-        <v>46046.049305555556</v>
+        <v>46270.375694444447</v>
       </c>
       <c r="B193" t="s">
-        <v>401</v>
+        <v>580</v>
       </c>
       <c r="C193" t="s">
-        <v>402</v>
+        <v>581</v>
       </c>
       <c r="D193" t="s">
-        <v>403</v>
+        <v>582</v>
       </c>
       <c r="E193" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
-        <v>46270.375694444447</v>
+        <v>46267.304861111108</v>
       </c>
       <c r="B194" t="s">
-        <v>404</v>
+        <v>583</v>
       </c>
       <c r="C194" t="s">
-        <v>405</v>
+        <v>584</v>
       </c>
       <c r="D194" t="s">
-        <v>406</v>
+        <v>585</v>
       </c>
       <c r="E194" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="L194">
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
-        <v>46267.304861111108</v>
+        <v>46053.940972222219</v>
       </c>
       <c r="B195" t="s">
-        <v>407</v>
+        <v>586</v>
       </c>
       <c r="C195" t="s">
-        <v>408</v>
+        <v>587</v>
       </c>
       <c r="D195" t="s">
-        <v>409</v>
+        <v>588</v>
       </c>
       <c r="E195" t="s">
-        <v>19</v>
-      </c>
-      <c r="L195">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
-        <v>46053.940972222219</v>
+        <v>46059.446527777778</v>
       </c>
       <c r="B196" t="s">
-        <v>410</v>
+        <v>589</v>
       </c>
       <c r="C196" t="s">
-        <v>411</v>
+        <v>590</v>
       </c>
       <c r="D196" t="s">
-        <v>412</v>
+        <v>591</v>
       </c>
       <c r="E196" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
-        <v>46059.446527777778</v>
+        <v>46061.826388888891</v>
       </c>
       <c r="B197" t="s">
-        <v>413</v>
+        <v>592</v>
       </c>
       <c r="C197" t="s">
-        <v>414</v>
+        <v>593</v>
       </c>
       <c r="D197" t="s">
-        <v>415</v>
+        <v>594</v>
       </c>
       <c r="E197" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L197">
         <v>1</v>
@@ -6555,19 +7069,19 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
-        <v>46061.826388888891</v>
+        <v>46053.894444444442</v>
       </c>
       <c r="B198" t="s">
-        <v>416</v>
+        <v>595</v>
       </c>
       <c r="C198" t="s">
-        <v>417</v>
+        <v>596</v>
       </c>
       <c r="D198" t="s">
-        <v>418</v>
+        <v>597</v>
       </c>
       <c r="E198" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L198">
         <v>1</v>
@@ -6575,56 +7089,56 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
-        <v>46053.894444444442</v>
+        <v>46058.756249999999</v>
       </c>
       <c r="B199" t="s">
-        <v>419</v>
+        <v>595</v>
       </c>
       <c r="C199" t="s">
-        <v>420</v>
+        <v>598</v>
       </c>
       <c r="D199" t="s">
-        <v>421</v>
+        <v>599</v>
       </c>
       <c r="E199" t="s">
-        <v>13</v>
-      </c>
-      <c r="L199">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
-        <v>46058.756249999999</v>
+        <v>46059.551388888889</v>
       </c>
       <c r="B200" t="s">
-        <v>419</v>
+        <v>600</v>
       </c>
       <c r="C200" t="s">
-        <v>422</v>
+        <v>601</v>
       </c>
       <c r="D200" t="s">
-        <v>423</v>
+        <v>602</v>
       </c>
       <c r="E200" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
-        <v>46059.551388888889</v>
+        <v>46061.82708333333</v>
       </c>
       <c r="B201" t="s">
-        <v>424</v>
+        <v>603</v>
       </c>
       <c r="C201" t="s">
-        <v>425</v>
+        <v>604</v>
       </c>
       <c r="D201" t="s">
-        <v>426</v>
+        <v>605</v>
       </c>
       <c r="E201" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L201">
         <v>1</v>
@@ -6632,19 +7146,19 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
-        <v>46061.82708333333</v>
+        <v>46061.97152777778</v>
       </c>
       <c r="B202" t="s">
-        <v>427</v>
+        <v>606</v>
       </c>
       <c r="C202" t="s">
-        <v>428</v>
+        <v>607</v>
       </c>
       <c r="D202" t="s">
-        <v>429</v>
+        <v>608</v>
       </c>
       <c r="E202" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L202">
         <v>1</v>
@@ -6652,19 +7166,19 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
-        <v>46061.97152777778</v>
+        <v>46058.798611111109</v>
       </c>
       <c r="B203" t="s">
-        <v>430</v>
+        <v>609</v>
       </c>
       <c r="C203" t="s">
-        <v>431</v>
+        <v>610</v>
       </c>
       <c r="D203" t="s">
-        <v>432</v>
+        <v>611</v>
       </c>
       <c r="E203" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L203">
         <v>1</v>
@@ -6672,19 +7186,19 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
-        <v>46058.798611111109</v>
+        <v>46045.5</v>
       </c>
       <c r="B204" t="s">
-        <v>433</v>
+        <v>612</v>
       </c>
       <c r="C204" t="s">
-        <v>434</v>
+        <v>613</v>
       </c>
       <c r="D204" t="s">
-        <v>435</v>
+        <v>614</v>
       </c>
       <c r="E204" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L204">
         <v>1</v>
@@ -6692,212 +7206,212 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
-        <v>46045.5</v>
+        <v>46061.47152777778</v>
       </c>
       <c r="B205" t="s">
-        <v>436</v>
+        <v>615</v>
       </c>
       <c r="C205" t="s">
-        <v>437</v>
+        <v>616</v>
       </c>
       <c r="D205" t="s">
-        <v>438</v>
+        <v>617</v>
       </c>
       <c r="E205" t="s">
-        <v>19</v>
-      </c>
-      <c r="L205">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
-        <v>46061.47152777778</v>
+        <v>46053.481249999997</v>
       </c>
       <c r="B206" t="s">
-        <v>439</v>
+        <v>618</v>
       </c>
       <c r="C206" t="s">
-        <v>440</v>
+        <v>619</v>
       </c>
       <c r="D206" t="s">
-        <v>441</v>
+        <v>620</v>
       </c>
       <c r="E206" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
-        <v>46053.481249999997</v>
+        <v>46045.490277777775</v>
       </c>
       <c r="B207" t="s">
-        <v>442</v>
+        <v>621</v>
       </c>
       <c r="C207" t="s">
-        <v>443</v>
+        <v>622</v>
       </c>
       <c r="D207" t="s">
-        <v>444</v>
+        <v>623</v>
       </c>
       <c r="E207" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A208" s="1">
-        <v>46045.490277777775</v>
-      </c>
       <c r="B208" t="s">
-        <v>445</v>
+        <v>624</v>
       </c>
       <c r="C208" t="s">
-        <v>446</v>
+        <v>625</v>
       </c>
       <c r="D208" t="s">
-        <v>447</v>
+        <v>626</v>
       </c>
       <c r="E208" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L208">
         <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A209" s="1">
+        <v>46045.722222222219</v>
+      </c>
       <c r="B209" t="s">
-        <v>448</v>
+        <v>627</v>
       </c>
       <c r="C209" t="s">
-        <v>449</v>
+        <v>628</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>629</v>
       </c>
       <c r="E209" t="s">
-        <v>19</v>
-      </c>
-      <c r="L209">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
-        <v>46045.722222222219</v>
+        <v>46045.496527777781</v>
       </c>
       <c r="B210" t="s">
-        <v>451</v>
+        <v>630</v>
       </c>
       <c r="C210" t="s">
-        <v>452</v>
+        <v>631</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>632</v>
       </c>
       <c r="E210" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
-        <v>46045.496527777781</v>
+        <v>46045.481249999997</v>
       </c>
       <c r="B211" t="s">
-        <v>454</v>
+        <v>633</v>
       </c>
       <c r="C211" t="s">
-        <v>455</v>
+        <v>634</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>635</v>
       </c>
       <c r="E211" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
-        <v>46045.481249999997</v>
+        <v>46061.01458333333</v>
       </c>
       <c r="B212" t="s">
-        <v>457</v>
+        <v>636</v>
       </c>
       <c r="C212" t="s">
-        <v>458</v>
+        <v>637</v>
       </c>
       <c r="D212" t="s">
-        <v>459</v>
+        <v>638</v>
       </c>
       <c r="E212" t="s">
-        <v>13</v>
-      </c>
-      <c r="L212">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
-        <v>46061.01458333333</v>
+        <v>46054.102777777778</v>
       </c>
       <c r="B213" t="s">
-        <v>460</v>
+        <v>639</v>
       </c>
       <c r="C213" t="s">
-        <v>461</v>
+        <v>640</v>
       </c>
       <c r="D213" t="s">
-        <v>462</v>
+        <v>641</v>
       </c>
       <c r="E213" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A214" s="1">
-        <v>46054.102777777778</v>
-      </c>
       <c r="B214" t="s">
-        <v>463</v>
+        <v>642</v>
       </c>
       <c r="C214" t="s">
-        <v>464</v>
+        <v>643</v>
       </c>
       <c r="D214" t="s">
-        <v>465</v>
+        <v>644</v>
       </c>
       <c r="E214" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>46274.375694444447</v>
+      </c>
       <c r="B215" t="s">
-        <v>466</v>
+        <v>645</v>
       </c>
       <c r="C215" t="s">
-        <v>467</v>
+        <v>646</v>
       </c>
       <c r="D215" t="s">
-        <v>468</v>
+        <v>647</v>
       </c>
       <c r="E215" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="L215">
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
-        <v>46274.375694444447</v>
+        <v>46048.520138888889</v>
       </c>
       <c r="B216" t="s">
-        <v>469</v>
+        <v>648</v>
       </c>
       <c r="C216" t="s">
-        <v>470</v>
+        <v>649</v>
       </c>
       <c r="D216" t="s">
-        <v>471</v>
+        <v>650</v>
       </c>
       <c r="E216" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L216">
         <v>1</v>
@@ -6905,19 +7419,22 @@
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
-        <v>46048.520138888889</v>
+        <v>46058.523611111108</v>
       </c>
       <c r="B217" t="s">
-        <v>472</v>
+        <v>651</v>
       </c>
       <c r="C217" t="s">
-        <v>473</v>
+        <v>652</v>
       </c>
       <c r="D217" t="s">
-        <v>474</v>
+        <v>653</v>
       </c>
       <c r="E217" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="F217" t="s">
+        <v>654</v>
       </c>
       <c r="L217">
         <v>1</v>
@@ -6925,22 +7442,22 @@
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
-        <v>46058.523611111108</v>
+        <v>46048.508333333331</v>
       </c>
       <c r="B218" t="s">
-        <v>475</v>
+        <v>655</v>
       </c>
       <c r="C218" t="s">
-        <v>476</v>
+        <v>656</v>
       </c>
       <c r="D218" t="s">
-        <v>477</v>
+        <v>657</v>
       </c>
       <c r="E218" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F218" t="s">
-        <v>478</v>
+        <v>46</v>
       </c>
       <c r="L218">
         <v>1</v>
@@ -6948,22 +7465,22 @@
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
-        <v>46048.508333333331</v>
+        <v>46056.454861111109</v>
       </c>
       <c r="B219" t="s">
-        <v>479</v>
+        <v>658</v>
       </c>
       <c r="C219" t="s">
-        <v>480</v>
+        <v>659</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>660</v>
       </c>
       <c r="E219" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F219" t="s">
-        <v>37</v>
+        <v>661</v>
       </c>
       <c r="L219">
         <v>1</v>
@@ -6971,82 +7488,82 @@
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
-        <v>46056.454861111109</v>
+        <v>46059.527083333334</v>
       </c>
       <c r="B220" t="s">
-        <v>482</v>
+        <v>662</v>
       </c>
       <c r="C220" t="s">
-        <v>483</v>
+        <v>663</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>664</v>
       </c>
       <c r="E220" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F220" t="s">
-        <v>485</v>
-      </c>
-      <c r="L220">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
-        <v>46059.527083333334</v>
+        <v>46058.688194444447</v>
       </c>
       <c r="B221" t="s">
-        <v>486</v>
+        <v>665</v>
       </c>
       <c r="C221" t="s">
-        <v>487</v>
+        <v>666</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>667</v>
       </c>
       <c r="E221" t="s">
-        <v>19</v>
-      </c>
-      <c r="F221" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
-        <v>46058.688194444447</v>
+        <v>46045.498611111114</v>
       </c>
       <c r="B222" t="s">
-        <v>489</v>
+        <v>668</v>
       </c>
       <c r="C222" t="s">
-        <v>490</v>
+        <v>669</v>
       </c>
       <c r="D222" t="s">
-        <v>491</v>
+        <v>670</v>
       </c>
       <c r="E222" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="F222" t="s">
+        <v>671</v>
+      </c>
+      <c r="L222">
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
-        <v>46045.498611111114</v>
+        <v>46058.897916666669</v>
       </c>
       <c r="B223" t="s">
-        <v>492</v>
+        <v>672</v>
       </c>
       <c r="C223" t="s">
-        <v>493</v>
+        <v>673</v>
       </c>
       <c r="D223" t="s">
-        <v>494</v>
+        <v>674</v>
       </c>
       <c r="E223" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F223" t="s">
-        <v>495</v>
+        <v>675</v>
       </c>
       <c r="L223">
         <v>1</v>
@@ -7054,22 +7571,19 @@
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
-        <v>46058.897916666669</v>
+        <v>46046.476388888892</v>
       </c>
       <c r="B224" t="s">
-        <v>496</v>
+        <v>676</v>
       </c>
       <c r="C224" t="s">
-        <v>497</v>
+        <v>677</v>
       </c>
       <c r="D224" t="s">
-        <v>498</v>
+        <v>678</v>
       </c>
       <c r="E224" t="s">
-        <v>19</v>
-      </c>
-      <c r="F224" t="s">
-        <v>499</v>
+        <v>22</v>
       </c>
       <c r="L224">
         <v>1</v>
@@ -7077,96 +7591,99 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
-        <v>46046.476388888892</v>
+        <v>46045.477777777778</v>
       </c>
       <c r="B225" t="s">
-        <v>500</v>
+        <v>679</v>
       </c>
       <c r="C225" t="s">
-        <v>501</v>
+        <v>680</v>
       </c>
       <c r="D225" t="s">
-        <v>502</v>
+        <v>681</v>
       </c>
       <c r="E225" t="s">
-        <v>19</v>
-      </c>
-      <c r="L225">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
-        <v>46045.477777777778</v>
+        <v>46045.50277777778</v>
       </c>
       <c r="B226" t="s">
-        <v>503</v>
+        <v>682</v>
       </c>
       <c r="C226" t="s">
-        <v>504</v>
+        <v>683</v>
       </c>
       <c r="D226" t="s">
-        <v>505</v>
+        <v>684</v>
       </c>
       <c r="E226" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="L226">
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
-        <v>46045.50277777778</v>
+        <v>46058.656944444447</v>
       </c>
       <c r="B227" t="s">
-        <v>506</v>
+        <v>685</v>
       </c>
       <c r="C227" t="s">
-        <v>507</v>
+        <v>686</v>
       </c>
       <c r="D227" t="s">
-        <v>508</v>
+        <v>687</v>
       </c>
       <c r="E227" t="s">
-        <v>13</v>
-      </c>
-      <c r="L227">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="F227" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A228" s="1">
-        <v>46058.656944444447</v>
-      </c>
       <c r="B228" t="s">
-        <v>509</v>
+        <v>688</v>
       </c>
       <c r="C228" t="s">
-        <v>510</v>
+        <v>689</v>
       </c>
       <c r="D228" t="s">
-        <v>511</v>
+        <v>690</v>
       </c>
       <c r="E228" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F228" t="s">
-        <v>14</v>
+        <v>691</v>
+      </c>
+      <c r="L228">
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A229" s="1">
+        <v>46267.276388888888</v>
+      </c>
       <c r="B229" t="s">
-        <v>512</v>
+        <v>692</v>
       </c>
       <c r="C229" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="D229" t="s">
-        <v>514</v>
+        <v>694</v>
       </c>
       <c r="E229" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F229" t="s">
-        <v>515</v>
+        <v>691</v>
       </c>
       <c r="L229">
         <v>1</v>
@@ -7174,125 +7691,125 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
-        <v>46267.276388888888</v>
+        <v>46059.396527777775</v>
       </c>
       <c r="B230" t="s">
-        <v>516</v>
+        <v>695</v>
       </c>
       <c r="C230" t="s">
-        <v>517</v>
+        <v>696</v>
       </c>
       <c r="D230" t="s">
-        <v>518</v>
+        <v>697</v>
       </c>
       <c r="E230" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F230" t="s">
-        <v>515</v>
-      </c>
-      <c r="L230">
-        <v>1</v>
+        <v>698</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
-        <v>46059.396527777775</v>
+        <v>46045.486111111109</v>
       </c>
       <c r="B231" t="s">
-        <v>519</v>
+        <v>699</v>
       </c>
       <c r="C231" t="s">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="D231" t="s">
-        <v>521</v>
+        <v>701</v>
       </c>
       <c r="E231" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F231" t="s">
-        <v>522</v>
+        <v>702</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
-        <v>46045.486111111109</v>
+        <v>46045.484027777777</v>
       </c>
       <c r="B232" t="s">
-        <v>523</v>
+        <v>703</v>
       </c>
       <c r="C232" t="s">
-        <v>524</v>
+        <v>704</v>
       </c>
       <c r="D232" t="s">
-        <v>525</v>
+        <v>705</v>
       </c>
       <c r="E232" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F232" t="s">
-        <v>526</v>
+        <v>15</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
-        <v>46045.484027777777</v>
+        <v>46047.488888888889</v>
       </c>
       <c r="B233" t="s">
-        <v>527</v>
+        <v>706</v>
       </c>
       <c r="C233" t="s">
-        <v>528</v>
+        <v>707</v>
       </c>
       <c r="D233" t="s">
-        <v>529</v>
+        <v>708</v>
       </c>
       <c r="E233" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F233" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
-        <v>46047.488888888889</v>
+        <v>46053.929861111108</v>
       </c>
       <c r="B234" t="s">
-        <v>530</v>
+        <v>706</v>
       </c>
       <c r="C234" t="s">
-        <v>531</v>
+        <v>709</v>
       </c>
       <c r="D234" t="s">
-        <v>532</v>
+        <v>710</v>
       </c>
       <c r="E234" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F234" t="s">
-        <v>14</v>
+        <v>711</v>
+      </c>
+      <c r="L234">
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
-        <v>46053.929861111108</v>
+        <v>46058.978472222225</v>
       </c>
       <c r="B235" t="s">
-        <v>530</v>
+        <v>706</v>
       </c>
       <c r="C235" t="s">
-        <v>533</v>
+        <v>712</v>
       </c>
       <c r="D235" t="s">
-        <v>534</v>
+        <v>713</v>
       </c>
       <c r="E235" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F235" t="s">
-        <v>535</v>
+        <v>714</v>
       </c>
       <c r="L235">
         <v>1</v>
@@ -7300,62 +7817,62 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
-        <v>46058.978472222225</v>
+        <v>46058.655555555553</v>
       </c>
       <c r="B236" t="s">
-        <v>530</v>
+        <v>715</v>
       </c>
       <c r="C236" t="s">
-        <v>536</v>
+        <v>716</v>
       </c>
       <c r="D236" t="s">
-        <v>537</v>
+        <v>717</v>
       </c>
       <c r="E236" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F236" t="s">
-        <v>538</v>
-      </c>
-      <c r="L236">
-        <v>1</v>
+        <v>718</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
-        <v>46058.655555555553</v>
+        <v>46267.370138888888</v>
       </c>
       <c r="B237" t="s">
-        <v>539</v>
+        <v>719</v>
       </c>
       <c r="C237" t="s">
-        <v>540</v>
+        <v>720</v>
       </c>
       <c r="D237" t="s">
-        <v>541</v>
+        <v>721</v>
       </c>
       <c r="E237" t="s">
-        <v>19</v>
-      </c>
-      <c r="F237" t="s">
-        <v>542</v>
+        <v>22</v>
+      </c>
+      <c r="L237">
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
-        <v>46267.370138888888</v>
+        <v>46057.644444444442</v>
       </c>
       <c r="B238" t="s">
-        <v>543</v>
+        <v>722</v>
       </c>
       <c r="C238" t="s">
-        <v>544</v>
+        <v>723</v>
       </c>
       <c r="D238" t="s">
-        <v>545</v>
+        <v>724</v>
       </c>
       <c r="E238" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="F238" t="s">
+        <v>725</v>
       </c>
       <c r="L238">
         <v>1</v>
@@ -7363,22 +7880,22 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
-        <v>46057.644444444442</v>
+        <v>46058.65625</v>
       </c>
       <c r="B239" t="s">
-        <v>546</v>
+        <v>726</v>
       </c>
       <c r="C239" t="s">
-        <v>547</v>
+        <v>727</v>
       </c>
       <c r="D239" t="s">
-        <v>548</v>
+        <v>728</v>
       </c>
       <c r="E239" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F239" t="s">
-        <v>549</v>
+        <v>729</v>
       </c>
       <c r="L239">
         <v>1</v>
@@ -7386,22 +7903,22 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
-        <v>46058.65625</v>
+        <v>46055.651388888888</v>
       </c>
       <c r="B240" t="s">
-        <v>550</v>
+        <v>730</v>
       </c>
       <c r="C240" t="s">
-        <v>551</v>
+        <v>731</v>
       </c>
       <c r="D240" t="s">
-        <v>552</v>
+        <v>732</v>
       </c>
       <c r="E240" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F240" t="s">
-        <v>553</v>
+        <v>733</v>
       </c>
       <c r="L240">
         <v>1</v>
@@ -7409,93 +7926,93 @@
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
-        <v>46055.651388888888</v>
+        <v>46058.657638888886</v>
       </c>
       <c r="B241" t="s">
-        <v>554</v>
+        <v>734</v>
       </c>
       <c r="C241" t="s">
-        <v>555</v>
+        <v>735</v>
       </c>
       <c r="D241" t="s">
-        <v>556</v>
+        <v>736</v>
       </c>
       <c r="E241" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F241" t="s">
-        <v>557</v>
-      </c>
-      <c r="L241">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A242" s="1">
-        <v>46058.657638888886</v>
-      </c>
       <c r="B242" t="s">
-        <v>558</v>
+        <v>737</v>
       </c>
       <c r="C242" t="s">
-        <v>559</v>
+        <v>738</v>
       </c>
       <c r="D242" t="s">
-        <v>560</v>
-      </c>
-      <c r="E242" t="s">
-        <v>19</v>
+        <v>739</v>
       </c>
       <c r="F242" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
-        <v>561</v>
-      </c>
-      <c r="C243" t="s">
-        <v>562</v>
+        <v>740</v>
       </c>
       <c r="D243" t="s">
-        <v>563</v>
+        <v>741</v>
+      </c>
+      <c r="E243" t="s">
+        <v>303</v>
       </c>
       <c r="F243" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>46236.995138888888</v>
+      </c>
       <c r="B244" t="s">
-        <v>564</v>
+        <v>742</v>
+      </c>
+      <c r="C244" t="s">
+        <v>356</v>
       </c>
       <c r="D244" t="s">
-        <v>565</v>
+        <v>743</v>
       </c>
       <c r="E244" t="s">
-        <v>213</v>
+        <v>14</v>
       </c>
       <c r="F244" t="s">
-        <v>37</v>
+        <v>744</v>
+      </c>
+      <c r="L244">
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
-        <v>46236.995138888888</v>
+        <v>46045.486805555556</v>
       </c>
       <c r="B245" t="s">
-        <v>566</v>
+        <v>745</v>
       </c>
       <c r="C245" t="s">
-        <v>249</v>
+        <v>746</v>
       </c>
       <c r="D245" t="s">
-        <v>567</v>
+        <v>747</v>
       </c>
       <c r="E245" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F245" t="s">
-        <v>568</v>
+        <v>748</v>
       </c>
       <c r="L245">
         <v>1</v>
@@ -7503,22 +8020,19 @@
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
-        <v>46045.486805555556</v>
+        <v>46045.48333333333</v>
       </c>
       <c r="B246" t="s">
-        <v>569</v>
+        <v>749</v>
       </c>
       <c r="C246" t="s">
-        <v>570</v>
+        <v>750</v>
       </c>
       <c r="D246" t="s">
-        <v>571</v>
+        <v>751</v>
       </c>
       <c r="E246" t="s">
-        <v>13</v>
-      </c>
-      <c r="F246" t="s">
-        <v>572</v>
+        <v>14</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -7526,19 +8040,19 @@
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
-        <v>46045.48333333333</v>
+        <v>46045.874305555553</v>
       </c>
       <c r="B247" t="s">
-        <v>573</v>
+        <v>752</v>
       </c>
       <c r="C247" t="s">
-        <v>574</v>
+        <v>753</v>
       </c>
       <c r="D247" t="s">
-        <v>575</v>
+        <v>754</v>
       </c>
       <c r="E247" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L247">
         <v>1</v>
@@ -7546,19 +8060,22 @@
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
-        <v>46045.874305555553</v>
+        <v>46045.741666666669</v>
       </c>
       <c r="B248" t="s">
-        <v>576</v>
+        <v>755</v>
       </c>
       <c r="C248" t="s">
-        <v>577</v>
+        <v>756</v>
       </c>
       <c r="D248" t="s">
-        <v>578</v>
+        <v>757</v>
       </c>
       <c r="E248" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="F248" t="s">
+        <v>758</v>
       </c>
       <c r="L248">
         <v>1</v>
@@ -7566,62 +8083,62 @@
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
-        <v>46045.741666666669</v>
+        <v>46056.272916666669</v>
       </c>
       <c r="B249" t="s">
-        <v>579</v>
+        <v>759</v>
       </c>
       <c r="C249" t="s">
-        <v>580</v>
+        <v>760</v>
       </c>
       <c r="D249" t="s">
-        <v>581</v>
+        <v>761</v>
       </c>
       <c r="E249" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F249" t="s">
-        <v>582</v>
-      </c>
-      <c r="L249">
-        <v>1</v>
+        <v>762</v>
       </c>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A250" s="1">
-        <v>46056.272916666669</v>
-      </c>
       <c r="B250" t="s">
-        <v>583</v>
+        <v>763</v>
       </c>
       <c r="C250" t="s">
-        <v>584</v>
+        <v>764</v>
       </c>
       <c r="D250" t="s">
-        <v>585</v>
+        <v>765</v>
       </c>
       <c r="E250" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F250" t="s">
-        <v>586</v>
+        <v>766</v>
+      </c>
+      <c r="L250">
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>46060.165972222225</v>
+      </c>
       <c r="B251" t="s">
-        <v>587</v>
+        <v>767</v>
       </c>
       <c r="C251" t="s">
-        <v>588</v>
+        <v>768</v>
       </c>
       <c r="D251" t="s">
-        <v>589</v>
+        <v>769</v>
       </c>
       <c r="E251" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F251" t="s">
-        <v>590</v>
+        <v>46</v>
       </c>
       <c r="L251">
         <v>1</v>
@@ -7629,128 +8146,128 @@
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
-        <v>46060.165972222225</v>
+        <v>46049.572916666664</v>
       </c>
       <c r="B252" t="s">
-        <v>591</v>
+        <v>770</v>
       </c>
       <c r="C252" t="s">
-        <v>592</v>
+        <v>771</v>
       </c>
       <c r="D252" t="s">
-        <v>593</v>
+        <v>772</v>
       </c>
       <c r="E252" t="s">
-        <v>13</v>
-      </c>
-      <c r="F252" t="s">
-        <v>37</v>
-      </c>
-      <c r="L252">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
-        <v>46049.572916666664</v>
+        <v>46053.948611111111</v>
       </c>
       <c r="B253" t="s">
-        <v>594</v>
+        <v>773</v>
       </c>
       <c r="C253" t="s">
-        <v>595</v>
+        <v>774</v>
       </c>
       <c r="D253" t="s">
-        <v>596</v>
+        <v>775</v>
       </c>
       <c r="E253" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="F253" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
-        <v>46053.948611111111</v>
+        <v>46058.525694444441</v>
       </c>
       <c r="B254" t="s">
-        <v>597</v>
+        <v>777</v>
       </c>
       <c r="C254" t="s">
-        <v>598</v>
+        <v>778</v>
       </c>
       <c r="D254" t="s">
-        <v>599</v>
+        <v>779</v>
       </c>
       <c r="E254" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F254" t="s">
-        <v>600</v>
+        <v>780</v>
+      </c>
+      <c r="L254">
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A255" s="1">
-        <v>46058.525694444441</v>
-      </c>
       <c r="B255" t="s">
-        <v>601</v>
+        <v>781</v>
       </c>
       <c r="C255" t="s">
-        <v>602</v>
+        <v>782</v>
       </c>
       <c r="D255" t="s">
-        <v>603</v>
+        <v>783</v>
       </c>
       <c r="E255" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F255" t="s">
-        <v>604</v>
+        <v>784</v>
       </c>
       <c r="L255">
         <v>1</v>
       </c>
+      <c r="M255" t="s">
+        <v>785</v>
+      </c>
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>46053.813194444447</v>
+      </c>
       <c r="B256" t="s">
-        <v>605</v>
+        <v>786</v>
       </c>
       <c r="C256" t="s">
-        <v>606</v>
+        <v>787</v>
       </c>
       <c r="D256" t="s">
-        <v>607</v>
+        <v>788</v>
       </c>
       <c r="E256" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F256" t="s">
-        <v>608</v>
+        <v>789</v>
       </c>
       <c r="L256">
         <v>1</v>
-      </c>
-      <c r="M256" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
-        <v>46053.813194444447</v>
+        <v>46061.484027777777</v>
       </c>
       <c r="B257" t="s">
-        <v>610</v>
+        <v>790</v>
       </c>
       <c r="C257" t="s">
-        <v>611</v>
+        <v>791</v>
       </c>
       <c r="D257" t="s">
-        <v>612</v>
+        <v>792</v>
       </c>
       <c r="E257" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F257" t="s">
-        <v>613</v>
+        <v>46</v>
       </c>
       <c r="L257">
         <v>1</v>
@@ -7758,22 +8275,22 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
-        <v>46061.484027777777</v>
+        <v>46060.685416666667</v>
       </c>
       <c r="B258" t="s">
-        <v>614</v>
+        <v>793</v>
       </c>
       <c r="C258" t="s">
-        <v>615</v>
+        <v>794</v>
       </c>
       <c r="D258" t="s">
-        <v>616</v>
+        <v>795</v>
       </c>
       <c r="E258" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F258" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="L258">
         <v>1</v>
@@ -7781,22 +8298,22 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
-        <v>46060.685416666667</v>
+        <v>46058.661111111112</v>
       </c>
       <c r="B259" t="s">
-        <v>617</v>
+        <v>796</v>
       </c>
       <c r="C259" t="s">
-        <v>618</v>
+        <v>797</v>
       </c>
       <c r="D259" t="s">
-        <v>619</v>
+        <v>798</v>
       </c>
       <c r="E259" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F259" t="s">
-        <v>40</v>
+        <v>799</v>
       </c>
       <c r="L259">
         <v>1</v>
@@ -7804,22 +8321,22 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
-        <v>46058.661111111112</v>
+        <v>46053.862500000003</v>
       </c>
       <c r="B260" t="s">
-        <v>620</v>
+        <v>800</v>
       </c>
       <c r="C260" t="s">
-        <v>621</v>
+        <v>801</v>
       </c>
       <c r="D260" t="s">
-        <v>622</v>
+        <v>802</v>
       </c>
       <c r="E260" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F260" t="s">
-        <v>623</v>
+        <v>129</v>
       </c>
       <c r="L260">
         <v>1</v>
@@ -7827,22 +8344,22 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
-        <v>46053.862500000003</v>
+        <v>46060.566666666666</v>
       </c>
       <c r="B261" t="s">
-        <v>624</v>
+        <v>803</v>
       </c>
       <c r="C261" t="s">
-        <v>625</v>
+        <v>804</v>
       </c>
       <c r="D261" t="s">
-        <v>626</v>
+        <v>805</v>
       </c>
       <c r="E261" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F261" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="L261">
         <v>1</v>
@@ -7850,45 +8367,42 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
-        <v>46060.566666666666</v>
+        <v>46061.265972222223</v>
       </c>
       <c r="B262" t="s">
-        <v>627</v>
+        <v>806</v>
       </c>
       <c r="C262" t="s">
-        <v>628</v>
+        <v>807</v>
       </c>
       <c r="D262" t="s">
-        <v>629</v>
+        <v>808</v>
       </c>
       <c r="E262" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F262" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="L262">
         <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A263" s="1">
-        <v>46061.265972222223</v>
-      </c>
       <c r="B263" t="s">
-        <v>630</v>
+        <v>809</v>
       </c>
       <c r="C263" t="s">
-        <v>631</v>
-      </c>
-      <c r="D263" t="s">
-        <v>632</v>
+        <v>810</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>811</v>
       </c>
       <c r="E263" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F263" t="s">
-        <v>96</v>
+        <v>812</v>
       </c>
       <c r="L263">
         <v>1</v>
@@ -7896,19 +8410,19 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B264" t="s">
-        <v>633</v>
+        <v>224</v>
       </c>
       <c r="C264" t="s">
-        <v>634</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>635</v>
+        <v>813</v>
+      </c>
+      <c r="D264" t="s">
+        <v>814</v>
       </c>
       <c r="E264" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F264" t="s">
-        <v>636</v>
+        <v>129</v>
       </c>
       <c r="L264">
         <v>1</v>
@@ -7916,77 +8430,34 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B265" t="s">
-        <v>159</v>
+        <v>272</v>
       </c>
       <c r="C265" t="s">
-        <v>637</v>
+        <v>815</v>
       </c>
       <c r="D265" t="s">
-        <v>638</v>
+        <v>816</v>
       </c>
       <c r="E265" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F265" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="L265">
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B266" t="s">
-        <v>193</v>
-      </c>
-      <c r="C266" t="s">
-        <v>639</v>
-      </c>
-      <c r="D266" t="s">
-        <v>640</v>
-      </c>
-      <c r="E266" t="s">
-        <v>13</v>
-      </c>
-      <c r="F266" t="s">
-        <v>37</v>
-      </c>
-      <c r="L266">
-        <v>1</v>
+    <row r="1048572" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E1048572" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{5F175408-23BB-4B48-9401-E77BFF250877}"/>
-    <hyperlink ref="D3:D65" r:id="rId2" display="edgaushome@gmail.com" xr:uid="{13CB21E4-EB61-4652-BA15-61C797464C7A}"/>
-    <hyperlink ref="D66" r:id="rId3" xr:uid="{7E44DFF6-12C4-469D-8725-1B48E16B80BC}"/>
-    <hyperlink ref="D130" r:id="rId4" xr:uid="{16774F35-BC3D-4F39-907A-B8C21CEEF30E}"/>
-    <hyperlink ref="D67:D129" r:id="rId5" display="edgaushome@gmail.com" xr:uid="{6C3C265A-FED3-4C5A-A1F1-B85C60448848}"/>
-    <hyperlink ref="D131:D138" r:id="rId6" display="edgaushome@gmail.com" xr:uid="{6C49DF23-25C0-44BC-A56C-957903A1A4B0}"/>
-    <hyperlink ref="D139" r:id="rId7" xr:uid="{6A7DE465-A92E-4F7B-BFF4-68F9802EB4F4}"/>
-    <hyperlink ref="D140:D154" r:id="rId8" display="edgaushome@gmail.com" xr:uid="{9BFB16E6-C517-4625-B582-3B9C947C5526}"/>
-    <hyperlink ref="D264" r:id="rId9" xr:uid="{43A79DF7-27C1-4F27-9D47-74D1FF01C7AD}"/>
-    <hyperlink ref="D155" r:id="rId10" xr:uid="{AE621EED-4EB5-4B55-ABFB-5A4D3B506A4B}"/>
-    <hyperlink ref="D156" r:id="rId11" xr:uid="{070B7FEE-2343-4EF2-90CF-F60FB36A397F}"/>
-    <hyperlink ref="D157" r:id="rId12" xr:uid="{CC8992F5-6C62-4D28-97CE-03271A29D9F2}"/>
-    <hyperlink ref="D158:D160" r:id="rId13" display="edgaushome@gmail.com" xr:uid="{EEA9D4BD-E818-44B6-87E0-17707AF4575E}"/>
-    <hyperlink ref="D161" r:id="rId14" xr:uid="{9B9325A7-FB46-44CB-A4B4-3AA4DC6BF12F}"/>
-    <hyperlink ref="D165" r:id="rId15" xr:uid="{0A5BCD82-26B1-4834-A341-C0078AB89FEA}"/>
-    <hyperlink ref="D169" r:id="rId16" xr:uid="{4E169591-9B6D-4EBE-AB5E-8E80032B0A14}"/>
-    <hyperlink ref="D173" r:id="rId17" xr:uid="{EE775438-1C86-46D7-B0DF-CA382CFAE0B2}"/>
-    <hyperlink ref="D177" r:id="rId18" xr:uid="{09390071-B1C7-4BB9-89A7-F318B29D09B7}"/>
-    <hyperlink ref="D162:D164" r:id="rId19" display="edgaushome@gmail.com" xr:uid="{1E3656F1-FDCB-437B-8D5A-DD4222AB94BF}"/>
-    <hyperlink ref="D166:D168" r:id="rId20" display="edgaushome@gmail.com" xr:uid="{820EBFBB-CB87-46D8-A647-CC9BADE9BE4E}"/>
-    <hyperlink ref="D170:D172" r:id="rId21" display="edgaushome@gmail.com" xr:uid="{384C621B-939D-4811-825C-3D56AAE314EF}"/>
-    <hyperlink ref="D174:D176" r:id="rId22" display="edgaushome@gmail.com" xr:uid="{EE440AEA-D061-487C-8F72-C1CCEA6FBEC6}"/>
-    <hyperlink ref="D178" r:id="rId23" xr:uid="{69CA7358-5568-48D6-87DE-1AECCC7D443F}"/>
-    <hyperlink ref="D179" r:id="rId24" xr:uid="{A61E9472-2F3F-4AEE-9B1A-542D1F0EC7FA}"/>
-    <hyperlink ref="D180:D182" r:id="rId25" display="edgaushome@gmail.com" xr:uid="{A36BD717-B958-437F-BFC1-6EAED252742C}"/>
-    <hyperlink ref="D183" r:id="rId26" xr:uid="{9AF37DBB-AA9A-4F9D-864D-55DD1028DFBC}"/>
-    <hyperlink ref="D187" r:id="rId27" xr:uid="{06C93E2B-2454-43CF-B1FC-9ED100C71293}"/>
-    <hyperlink ref="D184:D186" r:id="rId28" display="edgaushome@gmail.com" xr:uid="{9FE9FD83-5E5A-4761-8445-5F6C36D80A33}"/>
-    <hyperlink ref="D188" r:id="rId29" xr:uid="{FFE6E52F-1416-48FF-A0B4-B1B61B97A03A}"/>
+    <hyperlink ref="D263" r:id="rId1" xr:uid="{43A79DF7-27C1-4F27-9D47-74D1FF01C7AD}"/>
+    <hyperlink ref="D187" r:id="rId2" xr:uid="{BC7F591D-4078-4691-BC51-7186252BC120}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId30"/>
 </worksheet>
 </file>